--- a/templates/ERC000047/metadata_template_ERC000047.xlsx
+++ b/templates/ERC000047/metadata_template_ERC000047.xlsx
@@ -20,12 +20,12 @@
     <definedName name="assemblyquality">'cv_sample'!$AF$1:$AF$3</definedName>
     <definedName name="contaminationscreeninginput">'cv_sample'!$Z$1:$Z$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="reassemblypostbinning">'cv_sample'!$AD$1:$AD$2</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$G$1:$G$7</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="698">
   <si>
     <t>alias</t>
   </si>
@@ -451,6 +451,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1132,7 +1138,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>size fraction selected</t>
@@ -1354,9 +1360,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1375,6 +1378,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1576,6 +1582,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1585,9 +1594,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1627,7 +1633,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1696,6 +1702,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1771,6 +1780,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1792,6 +1804,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1837,6 +1852,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1849,6 +1867,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1858,9 +1879,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1885,6 +1903,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1945,12 +1966,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2107,7 +2128,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
@@ -2634,10 +2655,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2678,10 +2699,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2708,7 +2729,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2725,7 +2746,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2742,7 +2763,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2759,7 +2780,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2776,7 +2797,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2793,7 +2814,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2810,7 +2831,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2827,7 +2848,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2844,7 +2865,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2861,7 +2882,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2875,7 +2896,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2889,7 +2910,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2903,7 +2924,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2917,7 +2938,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2931,7 +2952,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2945,7 +2966,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2959,7 +2980,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2973,7 +2994,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2983,8 +3004,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2995,7 +3019,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3006,7 +3030,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3017,7 +3041,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3028,7 +3052,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3039,7 +3063,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3050,7 +3074,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3061,7 +3085,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3072,7 +3096,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3083,7 +3107,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3094,7 +3118,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3105,7 +3129,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3116,7 +3140,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3127,7 +3151,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3135,7 +3159,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3143,7 +3167,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3151,7 +3175,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3159,7 +3183,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3167,7 +3191,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3175,7 +3199,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3183,7 +3207,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3191,7 +3215,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3199,7 +3223,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3207,236 +3231,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3458,27 +3487,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3498,122 +3527,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3637,378 +3666,378 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2" spans="1:63" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -4038,1500 +4067,1525 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:AU289"/>
+  <dimension ref="G1:AU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:47">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Z1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AD1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AF1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AU1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="7:47">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Z2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AD2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AF2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AU2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="7:47">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AF3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AU3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="7:47">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AU4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="7:47">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AU5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="7:47">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AU6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="7:47">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AU7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="7:47">
       <c r="AU8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="7:47">
       <c r="AU9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="7:47">
       <c r="AU10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="7:47">
       <c r="AU11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="7:47">
       <c r="AU12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="7:47">
       <c r="AU13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="7:47">
       <c r="AU14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="7:47">
       <c r="AU15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="7:47">
       <c r="AU16" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="47:47">
       <c r="AU17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="47:47">
       <c r="AU18" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="47:47">
       <c r="AU19" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="47:47">
       <c r="AU20" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="47:47">
       <c r="AU21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="47:47">
       <c r="AU22" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="47:47">
       <c r="AU23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" spans="47:47">
       <c r="AU24" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="47:47">
       <c r="AU25" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" spans="47:47">
       <c r="AU26" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="27" spans="47:47">
       <c r="AU27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="47:47">
       <c r="AU28" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="47:47">
       <c r="AU29" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="47:47">
       <c r="AU30" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="31" spans="47:47">
       <c r="AU31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="47:47">
       <c r="AU32" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="47:47">
       <c r="AU33" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="47:47">
       <c r="AU34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="47:47">
       <c r="AU35" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="47:47">
       <c r="AU36" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="47:47">
       <c r="AU37" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="47:47">
       <c r="AU38" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" spans="47:47">
       <c r="AU39" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="47:47">
       <c r="AU40" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="47:47">
       <c r="AU41" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="47:47">
       <c r="AU42" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="47:47">
       <c r="AU43" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="44" spans="47:47">
       <c r="AU44" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="47:47">
       <c r="AU45" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="47:47">
       <c r="AU46" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" spans="47:47">
       <c r="AU47" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" spans="47:47">
       <c r="AU48" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="47:47">
       <c r="AU49" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" spans="47:47">
       <c r="AU50" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="47:47">
       <c r="AU51" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="47:47">
       <c r="AU52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="53" spans="47:47">
       <c r="AU53" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="54" spans="47:47">
       <c r="AU54" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="55" spans="47:47">
       <c r="AU55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56" spans="47:47">
       <c r="AU56" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" spans="47:47">
       <c r="AU57" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" spans="47:47">
       <c r="AU58" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="59" spans="47:47">
       <c r="AU59" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="60" spans="47:47">
       <c r="AU60" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="61" spans="47:47">
       <c r="AU61" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" spans="47:47">
       <c r="AU62" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" spans="47:47">
       <c r="AU63" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="47:47">
       <c r="AU64" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" spans="47:47">
       <c r="AU65" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66" spans="47:47">
       <c r="AU66" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67" spans="47:47">
       <c r="AU67" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="68" spans="47:47">
       <c r="AU68" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69" spans="47:47">
       <c r="AU69" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="47:47">
       <c r="AU70" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" spans="47:47">
       <c r="AU71" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="47:47">
       <c r="AU72" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="73" spans="47:47">
       <c r="AU73" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="74" spans="47:47">
       <c r="AU74" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75" spans="47:47">
       <c r="AU75" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="76" spans="47:47">
       <c r="AU76" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="47:47">
       <c r="AU77" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="78" spans="47:47">
       <c r="AU78" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="47:47">
       <c r="AU79" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="47:47">
       <c r="AU80" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="47:47">
       <c r="AU81" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="47:47">
       <c r="AU82" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="83" spans="47:47">
       <c r="AU83" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="47:47">
       <c r="AU84" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="85" spans="47:47">
       <c r="AU85" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="86" spans="47:47">
       <c r="AU86" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="87" spans="47:47">
       <c r="AU87" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="88" spans="47:47">
       <c r="AU88" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="89" spans="47:47">
       <c r="AU89" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="90" spans="47:47">
       <c r="AU90" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="91" spans="47:47">
       <c r="AU91" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="92" spans="47:47">
       <c r="AU92" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="93" spans="47:47">
       <c r="AU93" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="94" spans="47:47">
       <c r="AU94" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="95" spans="47:47">
       <c r="AU95" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="96" spans="47:47">
       <c r="AU96" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="97" spans="47:47">
       <c r="AU97" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="98" spans="47:47">
       <c r="AU98" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="99" spans="47:47">
       <c r="AU99" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="100" spans="47:47">
       <c r="AU100" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="101" spans="47:47">
       <c r="AU101" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="102" spans="47:47">
       <c r="AU102" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="103" spans="47:47">
       <c r="AU103" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" spans="47:47">
       <c r="AU104" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="105" spans="47:47">
       <c r="AU105" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="106" spans="47:47">
       <c r="AU106" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="107" spans="47:47">
       <c r="AU107" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="108" spans="47:47">
       <c r="AU108" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="109" spans="47:47">
       <c r="AU109" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="110" spans="47:47">
       <c r="AU110" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="111" spans="47:47">
       <c r="AU111" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="112" spans="47:47">
       <c r="AU112" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="113" spans="47:47">
       <c r="AU113" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="114" spans="47:47">
       <c r="AU114" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="115" spans="47:47">
       <c r="AU115" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="116" spans="47:47">
       <c r="AU116" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="47:47">
       <c r="AU117" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="118" spans="47:47">
       <c r="AU118" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="119" spans="47:47">
       <c r="AU119" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="120" spans="47:47">
       <c r="AU120" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="121" spans="47:47">
       <c r="AU121" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="122" spans="47:47">
       <c r="AU122" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="123" spans="47:47">
       <c r="AU123" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="124" spans="47:47">
       <c r="AU124" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="125" spans="47:47">
       <c r="AU125" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="126" spans="47:47">
       <c r="AU126" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="127" spans="47:47">
       <c r="AU127" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="128" spans="47:47">
       <c r="AU128" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="129" spans="47:47">
       <c r="AU129" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="130" spans="47:47">
       <c r="AU130" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="131" spans="47:47">
       <c r="AU131" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="132" spans="47:47">
       <c r="AU132" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="133" spans="47:47">
       <c r="AU133" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="134" spans="47:47">
       <c r="AU134" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="135" spans="47:47">
       <c r="AU135" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="136" spans="47:47">
       <c r="AU136" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="137" spans="47:47">
       <c r="AU137" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="138" spans="47:47">
       <c r="AU138" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="139" spans="47:47">
       <c r="AU139" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="140" spans="47:47">
       <c r="AU140" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="141" spans="47:47">
       <c r="AU141" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="142" spans="47:47">
       <c r="AU142" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="143" spans="47:47">
       <c r="AU143" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="144" spans="47:47">
       <c r="AU144" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="145" spans="47:47">
       <c r="AU145" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="146" spans="47:47">
       <c r="AU146" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="147" spans="47:47">
       <c r="AU147" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="148" spans="47:47">
       <c r="AU148" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="149" spans="47:47">
       <c r="AU149" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="150" spans="47:47">
       <c r="AU150" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="151" spans="47:47">
       <c r="AU151" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="152" spans="47:47">
       <c r="AU152" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="153" spans="47:47">
       <c r="AU153" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="154" spans="47:47">
       <c r="AU154" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="155" spans="47:47">
       <c r="AU155" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="156" spans="47:47">
       <c r="AU156" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="157" spans="47:47">
       <c r="AU157" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="158" spans="47:47">
       <c r="AU158" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="159" spans="47:47">
       <c r="AU159" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="160" spans="47:47">
       <c r="AU160" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="47:47">
       <c r="AU161" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162" spans="47:47">
       <c r="AU162" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="163" spans="47:47">
       <c r="AU163" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="164" spans="47:47">
       <c r="AU164" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="165" spans="47:47">
       <c r="AU165" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="166" spans="47:47">
       <c r="AU166" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="167" spans="47:47">
       <c r="AU167" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="168" spans="47:47">
       <c r="AU168" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="169" spans="47:47">
       <c r="AU169" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="170" spans="47:47">
       <c r="AU170" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="171" spans="47:47">
       <c r="AU171" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="172" spans="47:47">
       <c r="AU172" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="173" spans="47:47">
       <c r="AU173" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="174" spans="47:47">
       <c r="AU174" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="175" spans="47:47">
       <c r="AU175" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="176" spans="47:47">
       <c r="AU176" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="177" spans="47:47">
       <c r="AU177" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="178" spans="47:47">
       <c r="AU178" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="179" spans="47:47">
       <c r="AU179" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="180" spans="47:47">
       <c r="AU180" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="181" spans="47:47">
       <c r="AU181" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="182" spans="47:47">
       <c r="AU182" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="183" spans="47:47">
       <c r="AU183" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="184" spans="47:47">
       <c r="AU184" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="185" spans="47:47">
       <c r="AU185" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="186" spans="47:47">
       <c r="AU186" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="187" spans="47:47">
       <c r="AU187" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="188" spans="47:47">
       <c r="AU188" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="189" spans="47:47">
       <c r="AU189" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="190" spans="47:47">
       <c r="AU190" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="191" spans="47:47">
       <c r="AU191" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="192" spans="47:47">
       <c r="AU192" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="193" spans="47:47">
       <c r="AU193" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="194" spans="47:47">
       <c r="AU194" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="195" spans="47:47">
       <c r="AU195" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="196" spans="47:47">
       <c r="AU196" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="197" spans="47:47">
       <c r="AU197" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="198" spans="47:47">
       <c r="AU198" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="199" spans="47:47">
       <c r="AU199" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="200" spans="47:47">
       <c r="AU200" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="201" spans="47:47">
       <c r="AU201" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="202" spans="47:47">
       <c r="AU202" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="203" spans="47:47">
       <c r="AU203" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="204" spans="47:47">
       <c r="AU204" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="205" spans="47:47">
       <c r="AU205" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="206" spans="47:47">
       <c r="AU206" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="207" spans="47:47">
       <c r="AU207" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="208" spans="47:47">
       <c r="AU208" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="209" spans="47:47">
       <c r="AU209" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="210" spans="47:47">
       <c r="AU210" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="211" spans="47:47">
       <c r="AU211" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="212" spans="47:47">
       <c r="AU212" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="213" spans="47:47">
       <c r="AU213" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="214" spans="47:47">
       <c r="AU214" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="215" spans="47:47">
       <c r="AU215" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="216" spans="47:47">
       <c r="AU216" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="217" spans="47:47">
       <c r="AU217" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="218" spans="47:47">
       <c r="AU218" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="219" spans="47:47">
       <c r="AU219" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="220" spans="47:47">
       <c r="AU220" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="221" spans="47:47">
       <c r="AU221" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="222" spans="47:47">
       <c r="AU222" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="223" spans="47:47">
       <c r="AU223" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="224" spans="47:47">
       <c r="AU224" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="225" spans="47:47">
       <c r="AU225" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="226" spans="47:47">
       <c r="AU226" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="227" spans="47:47">
       <c r="AU227" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="228" spans="47:47">
       <c r="AU228" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="229" spans="47:47">
       <c r="AU229" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="230" spans="47:47">
       <c r="AU230" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="231" spans="47:47">
       <c r="AU231" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="232" spans="47:47">
       <c r="AU232" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="233" spans="47:47">
       <c r="AU233" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="234" spans="47:47">
       <c r="AU234" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="235" spans="47:47">
       <c r="AU235" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="236" spans="47:47">
       <c r="AU236" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="237" spans="47:47">
       <c r="AU237" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="238" spans="47:47">
       <c r="AU238" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="239" spans="47:47">
       <c r="AU239" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="240" spans="47:47">
       <c r="AU240" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="241" spans="47:47">
       <c r="AU241" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="242" spans="47:47">
       <c r="AU242" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="243" spans="47:47">
       <c r="AU243" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="244" spans="47:47">
       <c r="AU244" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="245" spans="47:47">
       <c r="AU245" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="246" spans="47:47">
       <c r="AU246" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="247" spans="47:47">
       <c r="AU247" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="248" spans="47:47">
       <c r="AU248" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="249" spans="47:47">
       <c r="AU249" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="250" spans="47:47">
       <c r="AU250" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="251" spans="47:47">
       <c r="AU251" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="252" spans="47:47">
       <c r="AU252" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="253" spans="47:47">
       <c r="AU253" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="254" spans="47:47">
       <c r="AU254" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="255" spans="47:47">
       <c r="AU255" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="256" spans="47:47">
       <c r="AU256" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="257" spans="47:47">
       <c r="AU257" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="258" spans="47:47">
       <c r="AU258" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="259" spans="47:47">
       <c r="AU259" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="260" spans="47:47">
       <c r="AU260" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="261" spans="47:47">
       <c r="AU261" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="262" spans="47:47">
       <c r="AU262" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="263" spans="47:47">
       <c r="AU263" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="264" spans="47:47">
       <c r="AU264" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="265" spans="47:47">
       <c r="AU265" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="266" spans="47:47">
       <c r="AU266" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="267" spans="47:47">
       <c r="AU267" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="268" spans="47:47">
       <c r="AU268" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="269" spans="47:47">
       <c r="AU269" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="270" spans="47:47">
       <c r="AU270" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="271" spans="47:47">
       <c r="AU271" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="272" spans="47:47">
       <c r="AU272" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="273" spans="47:47">
       <c r="AU273" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="274" spans="47:47">
       <c r="AU274" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="275" spans="47:47">
       <c r="AU275" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="276" spans="47:47">
       <c r="AU276" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="277" spans="47:47">
       <c r="AU277" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="278" spans="47:47">
       <c r="AU278" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="279" spans="47:47">
       <c r="AU279" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="280" spans="47:47">
       <c r="AU280" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="281" spans="47:47">
       <c r="AU281" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="282" spans="47:47">
       <c r="AU282" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="283" spans="47:47">
       <c r="AU283" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="284" spans="47:47">
       <c r="AU284" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="285" spans="47:47">
       <c r="AU285" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="286" spans="47:47">
       <c r="AU286" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="287" spans="47:47">
       <c r="AU287" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="288" spans="47:47">
       <c r="AU288" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="289" spans="47:47">
       <c r="AU289" t="s">
-        <v>656</v>
+        <v>658</v>
+      </c>
+    </row>
+    <row r="290" spans="47:47">
+      <c r="AU290" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="291" spans="47:47">
+      <c r="AU291" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="292" spans="47:47">
+      <c r="AU292" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="293" spans="47:47">
+      <c r="AU293" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="294" spans="47:47">
+      <c r="AU294" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000047/metadata_template_ERC000047.xlsx
+++ b/templates/ERC000047/metadata_template_ERC000047.xlsx
@@ -17,17 +17,17 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="assemblyquality">'cv_sample'!$AD$1:$AD$3</definedName>
-    <definedName name="contaminationscreeninginput">'cv_sample'!$X$1:$X$2</definedName>
+    <definedName name="assemblyquality">'cv_sample'!$AE$1:$AE$3</definedName>
+    <definedName name="contaminationscreeninginput">'cv_sample'!$Y$1:$Y$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AS$1:$AS$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AT$1:$AT$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="reassemblypostbinning">'cv_sample'!$AB$1:$AB$2</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$E$1:$E$7</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="reassemblypostbinning">'cv_sample'!$AC$1:$AC$2</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$F$1:$F$7</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="696">
   <si>
     <t>alias</t>
   </si>
@@ -451,6 +451,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -841,6 +847,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1342,9 +1354,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1363,6 +1372,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1564,6 +1576,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1573,9 +1588,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1615,7 +1627,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1684,6 +1696,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1759,6 +1774,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1780,6 +1798,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1825,6 +1846,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1837,6 +1861,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1846,9 +1873,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1873,6 +1897,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1933,10 +1960,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2622,10 +2649,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2666,10 +2693,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2713,7 +2740,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2730,7 +2757,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2747,7 +2774,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2764,7 +2791,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2781,7 +2808,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2798,7 +2825,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2815,7 +2842,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2832,7 +2859,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2849,7 +2876,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2863,7 +2890,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2877,7 +2904,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2891,7 +2918,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2905,7 +2932,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2919,7 +2946,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2933,7 +2960,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2947,7 +2974,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2961,7 +2988,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2971,8 +2998,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2983,7 +3013,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2994,7 +3024,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3005,7 +3035,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3016,7 +3046,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3027,7 +3057,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3038,7 +3068,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3049,7 +3079,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3060,7 +3090,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3071,7 +3101,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3082,7 +3112,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3093,7 +3123,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3104,7 +3134,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3115,7 +3145,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3123,7 +3153,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3131,7 +3161,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3139,7 +3169,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3147,7 +3177,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3155,7 +3185,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3163,7 +3193,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3171,7 +3201,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3179,7 +3209,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3187,7 +3217,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3195,236 +3225,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3446,27 +3481,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3486,122 +3521,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3611,13 +3646,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI2"/>
+  <dimension ref="A1:BJ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:62">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,386 +3660,392 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>303</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>319</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="2" spans="1:61" ht="150" customHeight="1">
+        <v>692</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>304</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>320</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>654</v>
+        <v>367</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>695</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
       <formula1>contaminationscreeninginput</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB3:AB101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
       <formula1>reassemblypostbinning</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>assemblyquality</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS3:AS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -4014,1500 +4055,1525 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:AS289"/>
+  <dimension ref="F1:AT294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:45">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>301</v>
-      </c>
-      <c r="X1" t="s">
-        <v>317</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>301</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>331</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="2" spans="5:45">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X2" t="s">
-        <v>318</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>302</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3" spans="5:45">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>333</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="4" spans="5:45">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="5" spans="5:45">
-      <c r="E5" t="s">
+    <row r="1" spans="6:46">
+      <c r="F1" t="s">
         <v>274</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="R1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>335</v>
+      </c>
+      <c r="AT1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="6" spans="5:45">
-      <c r="E6" t="s">
+    <row r="2" spans="6:46">
+      <c r="F2" t="s">
         <v>275</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="R2" t="s">
+        <v>306</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>306</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>336</v>
+      </c>
+      <c r="AT2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="7" spans="5:45">
-      <c r="E7" t="s">
+    <row r="3" spans="6:46">
+      <c r="F3" t="s">
         <v>276</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AE3" t="s">
+        <v>337</v>
+      </c>
+      <c r="AT3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="8" spans="5:45">
-      <c r="AS8" t="s">
+    <row r="4" spans="6:46">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="AT4" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="9" spans="5:45">
-      <c r="AS9" t="s">
+    <row r="5" spans="6:46">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AT5" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="10" spans="5:45">
-      <c r="AS10" t="s">
+    <row r="6" spans="6:46">
+      <c r="F6" t="s">
+        <v>279</v>
+      </c>
+      <c r="AT6" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="11" spans="5:45">
-      <c r="AS11" t="s">
+    <row r="7" spans="6:46">
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="AT7" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="12" spans="5:45">
-      <c r="AS12" t="s">
+    <row r="8" spans="6:46">
+      <c r="AT8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="13" spans="5:45">
-      <c r="AS13" t="s">
+    <row r="9" spans="6:46">
+      <c r="AT9" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="14" spans="5:45">
-      <c r="AS14" t="s">
+    <row r="10" spans="6:46">
+      <c r="AT10" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="5:45">
-      <c r="AS15" t="s">
+    <row r="11" spans="6:46">
+      <c r="AT11" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="16" spans="5:45">
-      <c r="AS16" t="s">
+    <row r="12" spans="6:46">
+      <c r="AT12" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="17" spans="45:45">
-      <c r="AS17" t="s">
+    <row r="13" spans="6:46">
+      <c r="AT13" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="18" spans="45:45">
-      <c r="AS18" t="s">
+    <row r="14" spans="6:46">
+      <c r="AT14" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="19" spans="45:45">
-      <c r="AS19" t="s">
+    <row r="15" spans="6:46">
+      <c r="AT15" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="20" spans="45:45">
-      <c r="AS20" t="s">
+    <row r="16" spans="6:46">
+      <c r="AT16" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="21" spans="45:45">
-      <c r="AS21" t="s">
+    <row r="17" spans="46:46">
+      <c r="AT17" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="22" spans="45:45">
-      <c r="AS22" t="s">
+    <row r="18" spans="46:46">
+      <c r="AT18" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="45:45">
-      <c r="AS23" t="s">
+    <row r="19" spans="46:46">
+      <c r="AT19" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="24" spans="45:45">
-      <c r="AS24" t="s">
+    <row r="20" spans="46:46">
+      <c r="AT20" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="25" spans="45:45">
-      <c r="AS25" t="s">
+    <row r="21" spans="46:46">
+      <c r="AT21" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="26" spans="45:45">
-      <c r="AS26" t="s">
+    <row r="22" spans="46:46">
+      <c r="AT22" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="27" spans="45:45">
-      <c r="AS27" t="s">
+    <row r="23" spans="46:46">
+      <c r="AT23" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="28" spans="45:45">
-      <c r="AS28" t="s">
+    <row r="24" spans="46:46">
+      <c r="AT24" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="29" spans="45:45">
-      <c r="AS29" t="s">
+    <row r="25" spans="46:46">
+      <c r="AT25" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="30" spans="45:45">
-      <c r="AS30" t="s">
+    <row r="26" spans="46:46">
+      <c r="AT26" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="31" spans="45:45">
-      <c r="AS31" t="s">
+    <row r="27" spans="46:46">
+      <c r="AT27" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="45:45">
-      <c r="AS32" t="s">
+    <row r="28" spans="46:46">
+      <c r="AT28" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="33" spans="45:45">
-      <c r="AS33" t="s">
+    <row r="29" spans="46:46">
+      <c r="AT29" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="34" spans="45:45">
-      <c r="AS34" t="s">
+    <row r="30" spans="46:46">
+      <c r="AT30" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="45:45">
-      <c r="AS35" t="s">
+    <row r="31" spans="46:46">
+      <c r="AT31" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="36" spans="45:45">
-      <c r="AS36" t="s">
+    <row r="32" spans="46:46">
+      <c r="AT32" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="37" spans="45:45">
-      <c r="AS37" t="s">
+    <row r="33" spans="46:46">
+      <c r="AT33" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="38" spans="45:45">
-      <c r="AS38" t="s">
+    <row r="34" spans="46:46">
+      <c r="AT34" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="39" spans="45:45">
-      <c r="AS39" t="s">
+    <row r="35" spans="46:46">
+      <c r="AT35" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="40" spans="45:45">
-      <c r="AS40" t="s">
+    <row r="36" spans="46:46">
+      <c r="AT36" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="41" spans="45:45">
-      <c r="AS41" t="s">
+    <row r="37" spans="46:46">
+      <c r="AT37" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="42" spans="45:45">
-      <c r="AS42" t="s">
+    <row r="38" spans="46:46">
+      <c r="AT38" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="43" spans="45:45">
-      <c r="AS43" t="s">
+    <row r="39" spans="46:46">
+      <c r="AT39" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="44" spans="45:45">
-      <c r="AS44" t="s">
+    <row r="40" spans="46:46">
+      <c r="AT40" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="45" spans="45:45">
-      <c r="AS45" t="s">
+    <row r="41" spans="46:46">
+      <c r="AT41" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="46" spans="45:45">
-      <c r="AS46" t="s">
+    <row r="42" spans="46:46">
+      <c r="AT42" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="47" spans="45:45">
-      <c r="AS47" t="s">
+    <row r="43" spans="46:46">
+      <c r="AT43" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="48" spans="45:45">
-      <c r="AS48" t="s">
+    <row r="44" spans="46:46">
+      <c r="AT44" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="49" spans="45:45">
-      <c r="AS49" t="s">
+    <row r="45" spans="46:46">
+      <c r="AT45" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="50" spans="45:45">
-      <c r="AS50" t="s">
+    <row r="46" spans="46:46">
+      <c r="AT46" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="51" spans="45:45">
-      <c r="AS51" t="s">
+    <row r="47" spans="46:46">
+      <c r="AT47" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="52" spans="45:45">
-      <c r="AS52" t="s">
+    <row r="48" spans="46:46">
+      <c r="AT48" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="53" spans="45:45">
-      <c r="AS53" t="s">
+    <row r="49" spans="46:46">
+      <c r="AT49" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="54" spans="45:45">
-      <c r="AS54" t="s">
+    <row r="50" spans="46:46">
+      <c r="AT50" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="55" spans="45:45">
-      <c r="AS55" t="s">
+    <row r="51" spans="46:46">
+      <c r="AT51" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="56" spans="45:45">
-      <c r="AS56" t="s">
+    <row r="52" spans="46:46">
+      <c r="AT52" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="57" spans="45:45">
-      <c r="AS57" t="s">
+    <row r="53" spans="46:46">
+      <c r="AT53" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="58" spans="45:45">
-      <c r="AS58" t="s">
+    <row r="54" spans="46:46">
+      <c r="AT54" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="59" spans="45:45">
-      <c r="AS59" t="s">
+    <row r="55" spans="46:46">
+      <c r="AT55" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="60" spans="45:45">
-      <c r="AS60" t="s">
+    <row r="56" spans="46:46">
+      <c r="AT56" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="61" spans="45:45">
-      <c r="AS61" t="s">
+    <row r="57" spans="46:46">
+      <c r="AT57" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="62" spans="45:45">
-      <c r="AS62" t="s">
+    <row r="58" spans="46:46">
+      <c r="AT58" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="63" spans="45:45">
-      <c r="AS63" t="s">
+    <row r="59" spans="46:46">
+      <c r="AT59" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="64" spans="45:45">
-      <c r="AS64" t="s">
+    <row r="60" spans="46:46">
+      <c r="AT60" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="65" spans="45:45">
-      <c r="AS65" t="s">
+    <row r="61" spans="46:46">
+      <c r="AT61" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="66" spans="45:45">
-      <c r="AS66" t="s">
+    <row r="62" spans="46:46">
+      <c r="AT62" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="67" spans="45:45">
-      <c r="AS67" t="s">
+    <row r="63" spans="46:46">
+      <c r="AT63" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="68" spans="45:45">
-      <c r="AS68" t="s">
+    <row r="64" spans="46:46">
+      <c r="AT64" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="69" spans="45:45">
-      <c r="AS69" t="s">
+    <row r="65" spans="46:46">
+      <c r="AT65" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="70" spans="45:45">
-      <c r="AS70" t="s">
+    <row r="66" spans="46:46">
+      <c r="AT66" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="71" spans="45:45">
-      <c r="AS71" t="s">
+    <row r="67" spans="46:46">
+      <c r="AT67" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="72" spans="45:45">
-      <c r="AS72" t="s">
+    <row r="68" spans="46:46">
+      <c r="AT68" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="73" spans="45:45">
-      <c r="AS73" t="s">
+    <row r="69" spans="46:46">
+      <c r="AT69" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="74" spans="45:45">
-      <c r="AS74" t="s">
+    <row r="70" spans="46:46">
+      <c r="AT70" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="75" spans="45:45">
-      <c r="AS75" t="s">
+    <row r="71" spans="46:46">
+      <c r="AT71" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="76" spans="45:45">
-      <c r="AS76" t="s">
+    <row r="72" spans="46:46">
+      <c r="AT72" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="77" spans="45:45">
-      <c r="AS77" t="s">
+    <row r="73" spans="46:46">
+      <c r="AT73" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="78" spans="45:45">
-      <c r="AS78" t="s">
+    <row r="74" spans="46:46">
+      <c r="AT74" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="79" spans="45:45">
-      <c r="AS79" t="s">
+    <row r="75" spans="46:46">
+      <c r="AT75" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="80" spans="45:45">
-      <c r="AS80" t="s">
+    <row r="76" spans="46:46">
+      <c r="AT76" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="81" spans="45:45">
-      <c r="AS81" t="s">
+    <row r="77" spans="46:46">
+      <c r="AT77" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="82" spans="45:45">
-      <c r="AS82" t="s">
+    <row r="78" spans="46:46">
+      <c r="AT78" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="83" spans="45:45">
-      <c r="AS83" t="s">
+    <row r="79" spans="46:46">
+      <c r="AT79" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="84" spans="45:45">
-      <c r="AS84" t="s">
+    <row r="80" spans="46:46">
+      <c r="AT80" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="85" spans="45:45">
-      <c r="AS85" t="s">
+    <row r="81" spans="46:46">
+      <c r="AT81" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="86" spans="45:45">
-      <c r="AS86" t="s">
+    <row r="82" spans="46:46">
+      <c r="AT82" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="87" spans="45:45">
-      <c r="AS87" t="s">
+    <row r="83" spans="46:46">
+      <c r="AT83" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="88" spans="45:45">
-      <c r="AS88" t="s">
+    <row r="84" spans="46:46">
+      <c r="AT84" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="89" spans="45:45">
-      <c r="AS89" t="s">
+    <row r="85" spans="46:46">
+      <c r="AT85" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="90" spans="45:45">
-      <c r="AS90" t="s">
+    <row r="86" spans="46:46">
+      <c r="AT86" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="91" spans="45:45">
-      <c r="AS91" t="s">
+    <row r="87" spans="46:46">
+      <c r="AT87" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="92" spans="45:45">
-      <c r="AS92" t="s">
+    <row r="88" spans="46:46">
+      <c r="AT88" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="93" spans="45:45">
-      <c r="AS93" t="s">
+    <row r="89" spans="46:46">
+      <c r="AT89" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="94" spans="45:45">
-      <c r="AS94" t="s">
+    <row r="90" spans="46:46">
+      <c r="AT90" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="95" spans="45:45">
-      <c r="AS95" t="s">
+    <row r="91" spans="46:46">
+      <c r="AT91" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="96" spans="45:45">
-      <c r="AS96" t="s">
+    <row r="92" spans="46:46">
+      <c r="AT92" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="97" spans="45:45">
-      <c r="AS97" t="s">
+    <row r="93" spans="46:46">
+      <c r="AT93" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="98" spans="45:45">
-      <c r="AS98" t="s">
+    <row r="94" spans="46:46">
+      <c r="AT94" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="99" spans="45:45">
-      <c r="AS99" t="s">
+    <row r="95" spans="46:46">
+      <c r="AT95" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="100" spans="45:45">
-      <c r="AS100" t="s">
+    <row r="96" spans="46:46">
+      <c r="AT96" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="101" spans="45:45">
-      <c r="AS101" t="s">
+    <row r="97" spans="46:46">
+      <c r="AT97" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="102" spans="45:45">
-      <c r="AS102" t="s">
+    <row r="98" spans="46:46">
+      <c r="AT98" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="103" spans="45:45">
-      <c r="AS103" t="s">
+    <row r="99" spans="46:46">
+      <c r="AT99" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="104" spans="45:45">
-      <c r="AS104" t="s">
+    <row r="100" spans="46:46">
+      <c r="AT100" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="105" spans="45:45">
-      <c r="AS105" t="s">
+    <row r="101" spans="46:46">
+      <c r="AT101" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="106" spans="45:45">
-      <c r="AS106" t="s">
+    <row r="102" spans="46:46">
+      <c r="AT102" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="107" spans="45:45">
-      <c r="AS107" t="s">
+    <row r="103" spans="46:46">
+      <c r="AT103" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="108" spans="45:45">
-      <c r="AS108" t="s">
+    <row r="104" spans="46:46">
+      <c r="AT104" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="109" spans="45:45">
-      <c r="AS109" t="s">
+    <row r="105" spans="46:46">
+      <c r="AT105" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="110" spans="45:45">
-      <c r="AS110" t="s">
+    <row r="106" spans="46:46">
+      <c r="AT106" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="111" spans="45:45">
-      <c r="AS111" t="s">
+    <row r="107" spans="46:46">
+      <c r="AT107" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="112" spans="45:45">
-      <c r="AS112" t="s">
+    <row r="108" spans="46:46">
+      <c r="AT108" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="113" spans="45:45">
-      <c r="AS113" t="s">
+    <row r="109" spans="46:46">
+      <c r="AT109" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="114" spans="45:45">
-      <c r="AS114" t="s">
+    <row r="110" spans="46:46">
+      <c r="AT110" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="115" spans="45:45">
-      <c r="AS115" t="s">
+    <row r="111" spans="46:46">
+      <c r="AT111" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="116" spans="45:45">
-      <c r="AS116" t="s">
+    <row r="112" spans="46:46">
+      <c r="AT112" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="117" spans="45:45">
-      <c r="AS117" t="s">
+    <row r="113" spans="46:46">
+      <c r="AT113" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="118" spans="45:45">
-      <c r="AS118" t="s">
+    <row r="114" spans="46:46">
+      <c r="AT114" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="119" spans="45:45">
-      <c r="AS119" t="s">
+    <row r="115" spans="46:46">
+      <c r="AT115" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="120" spans="45:45">
-      <c r="AS120" t="s">
+    <row r="116" spans="46:46">
+      <c r="AT116" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="121" spans="45:45">
-      <c r="AS121" t="s">
+    <row r="117" spans="46:46">
+      <c r="AT117" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="122" spans="45:45">
-      <c r="AS122" t="s">
+    <row r="118" spans="46:46">
+      <c r="AT118" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="123" spans="45:45">
-      <c r="AS123" t="s">
+    <row r="119" spans="46:46">
+      <c r="AT119" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="124" spans="45:45">
-      <c r="AS124" t="s">
+    <row r="120" spans="46:46">
+      <c r="AT120" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="125" spans="45:45">
-      <c r="AS125" t="s">
+    <row r="121" spans="46:46">
+      <c r="AT121" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="126" spans="45:45">
-      <c r="AS126" t="s">
+    <row r="122" spans="46:46">
+      <c r="AT122" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="127" spans="45:45">
-      <c r="AS127" t="s">
+    <row r="123" spans="46:46">
+      <c r="AT123" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="128" spans="45:45">
-      <c r="AS128" t="s">
+    <row r="124" spans="46:46">
+      <c r="AT124" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="129" spans="45:45">
-      <c r="AS129" t="s">
+    <row r="125" spans="46:46">
+      <c r="AT125" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="130" spans="45:45">
-      <c r="AS130" t="s">
+    <row r="126" spans="46:46">
+      <c r="AT126" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="131" spans="45:45">
-      <c r="AS131" t="s">
+    <row r="127" spans="46:46">
+      <c r="AT127" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="132" spans="45:45">
-      <c r="AS132" t="s">
+    <row r="128" spans="46:46">
+      <c r="AT128" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="133" spans="45:45">
-      <c r="AS133" t="s">
+    <row r="129" spans="46:46">
+      <c r="AT129" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="134" spans="45:45">
-      <c r="AS134" t="s">
+    <row r="130" spans="46:46">
+      <c r="AT130" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="135" spans="45:45">
-      <c r="AS135" t="s">
+    <row r="131" spans="46:46">
+      <c r="AT131" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="136" spans="45:45">
-      <c r="AS136" t="s">
+    <row r="132" spans="46:46">
+      <c r="AT132" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="137" spans="45:45">
-      <c r="AS137" t="s">
+    <row r="133" spans="46:46">
+      <c r="AT133" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="138" spans="45:45">
-      <c r="AS138" t="s">
+    <row r="134" spans="46:46">
+      <c r="AT134" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="139" spans="45:45">
-      <c r="AS139" t="s">
+    <row r="135" spans="46:46">
+      <c r="AT135" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="140" spans="45:45">
-      <c r="AS140" t="s">
+    <row r="136" spans="46:46">
+      <c r="AT136" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="141" spans="45:45">
-      <c r="AS141" t="s">
+    <row r="137" spans="46:46">
+      <c r="AT137" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="142" spans="45:45">
-      <c r="AS142" t="s">
+    <row r="138" spans="46:46">
+      <c r="AT138" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="143" spans="45:45">
-      <c r="AS143" t="s">
+    <row r="139" spans="46:46">
+      <c r="AT139" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="144" spans="45:45">
-      <c r="AS144" t="s">
+    <row r="140" spans="46:46">
+      <c r="AT140" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="145" spans="45:45">
-      <c r="AS145" t="s">
+    <row r="141" spans="46:46">
+      <c r="AT141" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="146" spans="45:45">
-      <c r="AS146" t="s">
+    <row r="142" spans="46:46">
+      <c r="AT142" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="147" spans="45:45">
-      <c r="AS147" t="s">
+    <row r="143" spans="46:46">
+      <c r="AT143" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="148" spans="45:45">
-      <c r="AS148" t="s">
+    <row r="144" spans="46:46">
+      <c r="AT144" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="149" spans="45:45">
-      <c r="AS149" t="s">
+    <row r="145" spans="46:46">
+      <c r="AT145" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="150" spans="45:45">
-      <c r="AS150" t="s">
+    <row r="146" spans="46:46">
+      <c r="AT146" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="151" spans="45:45">
-      <c r="AS151" t="s">
+    <row r="147" spans="46:46">
+      <c r="AT147" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="152" spans="45:45">
-      <c r="AS152" t="s">
+    <row r="148" spans="46:46">
+      <c r="AT148" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="153" spans="45:45">
-      <c r="AS153" t="s">
+    <row r="149" spans="46:46">
+      <c r="AT149" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="154" spans="45:45">
-      <c r="AS154" t="s">
+    <row r="150" spans="46:46">
+      <c r="AT150" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="155" spans="45:45">
-      <c r="AS155" t="s">
+    <row r="151" spans="46:46">
+      <c r="AT151" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="156" spans="45:45">
-      <c r="AS156" t="s">
+    <row r="152" spans="46:46">
+      <c r="AT152" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="157" spans="45:45">
-      <c r="AS157" t="s">
+    <row r="153" spans="46:46">
+      <c r="AT153" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="158" spans="45:45">
-      <c r="AS158" t="s">
+    <row r="154" spans="46:46">
+      <c r="AT154" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="159" spans="45:45">
-      <c r="AS159" t="s">
+    <row r="155" spans="46:46">
+      <c r="AT155" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="160" spans="45:45">
-      <c r="AS160" t="s">
+    <row r="156" spans="46:46">
+      <c r="AT156" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="161" spans="45:45">
-      <c r="AS161" t="s">
+    <row r="157" spans="46:46">
+      <c r="AT157" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="162" spans="45:45">
-      <c r="AS162" t="s">
+    <row r="158" spans="46:46">
+      <c r="AT158" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="163" spans="45:45">
-      <c r="AS163" t="s">
+    <row r="159" spans="46:46">
+      <c r="AT159" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="164" spans="45:45">
-      <c r="AS164" t="s">
+    <row r="160" spans="46:46">
+      <c r="AT160" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="45:45">
-      <c r="AS165" t="s">
+    <row r="161" spans="46:46">
+      <c r="AT161" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="166" spans="45:45">
-      <c r="AS166" t="s">
+    <row r="162" spans="46:46">
+      <c r="AT162" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="167" spans="45:45">
-      <c r="AS167" t="s">
+    <row r="163" spans="46:46">
+      <c r="AT163" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="168" spans="45:45">
-      <c r="AS168" t="s">
+    <row r="164" spans="46:46">
+      <c r="AT164" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="169" spans="45:45">
-      <c r="AS169" t="s">
+    <row r="165" spans="46:46">
+      <c r="AT165" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="170" spans="45:45">
-      <c r="AS170" t="s">
+    <row r="166" spans="46:46">
+      <c r="AT166" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="171" spans="45:45">
-      <c r="AS171" t="s">
+    <row r="167" spans="46:46">
+      <c r="AT167" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="172" spans="45:45">
-      <c r="AS172" t="s">
+    <row r="168" spans="46:46">
+      <c r="AT168" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="173" spans="45:45">
-      <c r="AS173" t="s">
+    <row r="169" spans="46:46">
+      <c r="AT169" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="174" spans="45:45">
-      <c r="AS174" t="s">
+    <row r="170" spans="46:46">
+      <c r="AT170" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="175" spans="45:45">
-      <c r="AS175" t="s">
+    <row r="171" spans="46:46">
+      <c r="AT171" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="176" spans="45:45">
-      <c r="AS176" t="s">
+    <row r="172" spans="46:46">
+      <c r="AT172" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="177" spans="45:45">
-      <c r="AS177" t="s">
+    <row r="173" spans="46:46">
+      <c r="AT173" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="178" spans="45:45">
-      <c r="AS178" t="s">
+    <row r="174" spans="46:46">
+      <c r="AT174" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="179" spans="45:45">
-      <c r="AS179" t="s">
+    <row r="175" spans="46:46">
+      <c r="AT175" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="180" spans="45:45">
-      <c r="AS180" t="s">
+    <row r="176" spans="46:46">
+      <c r="AT176" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="181" spans="45:45">
-      <c r="AS181" t="s">
+    <row r="177" spans="46:46">
+      <c r="AT177" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="182" spans="45:45">
-      <c r="AS182" t="s">
+    <row r="178" spans="46:46">
+      <c r="AT178" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="183" spans="45:45">
-      <c r="AS183" t="s">
+    <row r="179" spans="46:46">
+      <c r="AT179" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="184" spans="45:45">
-      <c r="AS184" t="s">
+    <row r="180" spans="46:46">
+      <c r="AT180" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="185" spans="45:45">
-      <c r="AS185" t="s">
+    <row r="181" spans="46:46">
+      <c r="AT181" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="186" spans="45:45">
-      <c r="AS186" t="s">
+    <row r="182" spans="46:46">
+      <c r="AT182" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="187" spans="45:45">
-      <c r="AS187" t="s">
+    <row r="183" spans="46:46">
+      <c r="AT183" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="188" spans="45:45">
-      <c r="AS188" t="s">
+    <row r="184" spans="46:46">
+      <c r="AT184" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="189" spans="45:45">
-      <c r="AS189" t="s">
+    <row r="185" spans="46:46">
+      <c r="AT185" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="190" spans="45:45">
-      <c r="AS190" t="s">
+    <row r="186" spans="46:46">
+      <c r="AT186" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="191" spans="45:45">
-      <c r="AS191" t="s">
+    <row r="187" spans="46:46">
+      <c r="AT187" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="192" spans="45:45">
-      <c r="AS192" t="s">
+    <row r="188" spans="46:46">
+      <c r="AT188" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="193" spans="45:45">
-      <c r="AS193" t="s">
+    <row r="189" spans="46:46">
+      <c r="AT189" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="194" spans="45:45">
-      <c r="AS194" t="s">
+    <row r="190" spans="46:46">
+      <c r="AT190" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="195" spans="45:45">
-      <c r="AS195" t="s">
+    <row r="191" spans="46:46">
+      <c r="AT191" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="196" spans="45:45">
-      <c r="AS196" t="s">
+    <row r="192" spans="46:46">
+      <c r="AT192" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="197" spans="45:45">
-      <c r="AS197" t="s">
+    <row r="193" spans="46:46">
+      <c r="AT193" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="198" spans="45:45">
-      <c r="AS198" t="s">
+    <row r="194" spans="46:46">
+      <c r="AT194" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="199" spans="45:45">
-      <c r="AS199" t="s">
+    <row r="195" spans="46:46">
+      <c r="AT195" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="200" spans="45:45">
-      <c r="AS200" t="s">
+    <row r="196" spans="46:46">
+      <c r="AT196" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="201" spans="45:45">
-      <c r="AS201" t="s">
+    <row r="197" spans="46:46">
+      <c r="AT197" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="202" spans="45:45">
-      <c r="AS202" t="s">
+    <row r="198" spans="46:46">
+      <c r="AT198" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="203" spans="45:45">
-      <c r="AS203" t="s">
+    <row r="199" spans="46:46">
+      <c r="AT199" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="204" spans="45:45">
-      <c r="AS204" t="s">
+    <row r="200" spans="46:46">
+      <c r="AT200" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="205" spans="45:45">
-      <c r="AS205" t="s">
+    <row r="201" spans="46:46">
+      <c r="AT201" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="206" spans="45:45">
-      <c r="AS206" t="s">
+    <row r="202" spans="46:46">
+      <c r="AT202" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="207" spans="45:45">
-      <c r="AS207" t="s">
+    <row r="203" spans="46:46">
+      <c r="AT203" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="208" spans="45:45">
-      <c r="AS208" t="s">
+    <row r="204" spans="46:46">
+      <c r="AT204" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="209" spans="45:45">
-      <c r="AS209" t="s">
+    <row r="205" spans="46:46">
+      <c r="AT205" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="210" spans="45:45">
-      <c r="AS210" t="s">
+    <row r="206" spans="46:46">
+      <c r="AT206" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="211" spans="45:45">
-      <c r="AS211" t="s">
+    <row r="207" spans="46:46">
+      <c r="AT207" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="212" spans="45:45">
-      <c r="AS212" t="s">
+    <row r="208" spans="46:46">
+      <c r="AT208" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="213" spans="45:45">
-      <c r="AS213" t="s">
+    <row r="209" spans="46:46">
+      <c r="AT209" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="214" spans="45:45">
-      <c r="AS214" t="s">
+    <row r="210" spans="46:46">
+      <c r="AT210" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="215" spans="45:45">
-      <c r="AS215" t="s">
+    <row r="211" spans="46:46">
+      <c r="AT211" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="216" spans="45:45">
-      <c r="AS216" t="s">
+    <row r="212" spans="46:46">
+      <c r="AT212" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="217" spans="45:45">
-      <c r="AS217" t="s">
+    <row r="213" spans="46:46">
+      <c r="AT213" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="218" spans="45:45">
-      <c r="AS218" t="s">
+    <row r="214" spans="46:46">
+      <c r="AT214" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="219" spans="45:45">
-      <c r="AS219" t="s">
+    <row r="215" spans="46:46">
+      <c r="AT215" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="220" spans="45:45">
-      <c r="AS220" t="s">
+    <row r="216" spans="46:46">
+      <c r="AT216" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="221" spans="45:45">
-      <c r="AS221" t="s">
+    <row r="217" spans="46:46">
+      <c r="AT217" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="222" spans="45:45">
-      <c r="AS222" t="s">
+    <row r="218" spans="46:46">
+      <c r="AT218" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="223" spans="45:45">
-      <c r="AS223" t="s">
+    <row r="219" spans="46:46">
+      <c r="AT219" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="224" spans="45:45">
-      <c r="AS224" t="s">
+    <row r="220" spans="46:46">
+      <c r="AT220" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="225" spans="45:45">
-      <c r="AS225" t="s">
+    <row r="221" spans="46:46">
+      <c r="AT221" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="226" spans="45:45">
-      <c r="AS226" t="s">
+    <row r="222" spans="46:46">
+      <c r="AT222" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="227" spans="45:45">
-      <c r="AS227" t="s">
+    <row r="223" spans="46:46">
+      <c r="AT223" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="228" spans="45:45">
-      <c r="AS228" t="s">
+    <row r="224" spans="46:46">
+      <c r="AT224" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="229" spans="45:45">
-      <c r="AS229" t="s">
+    <row r="225" spans="46:46">
+      <c r="AT225" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="230" spans="45:45">
-      <c r="AS230" t="s">
+    <row r="226" spans="46:46">
+      <c r="AT226" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="231" spans="45:45">
-      <c r="AS231" t="s">
+    <row r="227" spans="46:46">
+      <c r="AT227" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="232" spans="45:45">
-      <c r="AS232" t="s">
+    <row r="228" spans="46:46">
+      <c r="AT228" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="233" spans="45:45">
-      <c r="AS233" t="s">
+    <row r="229" spans="46:46">
+      <c r="AT229" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="234" spans="45:45">
-      <c r="AS234" t="s">
+    <row r="230" spans="46:46">
+      <c r="AT230" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="235" spans="45:45">
-      <c r="AS235" t="s">
+    <row r="231" spans="46:46">
+      <c r="AT231" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="236" spans="45:45">
-      <c r="AS236" t="s">
+    <row r="232" spans="46:46">
+      <c r="AT232" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="237" spans="45:45">
-      <c r="AS237" t="s">
+    <row r="233" spans="46:46">
+      <c r="AT233" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="238" spans="45:45">
-      <c r="AS238" t="s">
+    <row r="234" spans="46:46">
+      <c r="AT234" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="239" spans="45:45">
-      <c r="AS239" t="s">
+    <row r="235" spans="46:46">
+      <c r="AT235" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="240" spans="45:45">
-      <c r="AS240" t="s">
+    <row r="236" spans="46:46">
+      <c r="AT236" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="241" spans="45:45">
-      <c r="AS241" t="s">
+    <row r="237" spans="46:46">
+      <c r="AT237" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="242" spans="45:45">
-      <c r="AS242" t="s">
+    <row r="238" spans="46:46">
+      <c r="AT238" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="243" spans="45:45">
-      <c r="AS243" t="s">
+    <row r="239" spans="46:46">
+      <c r="AT239" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="244" spans="45:45">
-      <c r="AS244" t="s">
+    <row r="240" spans="46:46">
+      <c r="AT240" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="245" spans="45:45">
-      <c r="AS245" t="s">
+    <row r="241" spans="46:46">
+      <c r="AT241" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="246" spans="45:45">
-      <c r="AS246" t="s">
+    <row r="242" spans="46:46">
+      <c r="AT242" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="247" spans="45:45">
-      <c r="AS247" t="s">
+    <row r="243" spans="46:46">
+      <c r="AT243" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="248" spans="45:45">
-      <c r="AS248" t="s">
+    <row r="244" spans="46:46">
+      <c r="AT244" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="249" spans="45:45">
-      <c r="AS249" t="s">
+    <row r="245" spans="46:46">
+      <c r="AT245" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="250" spans="45:45">
-      <c r="AS250" t="s">
+    <row r="246" spans="46:46">
+      <c r="AT246" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="251" spans="45:45">
-      <c r="AS251" t="s">
+    <row r="247" spans="46:46">
+      <c r="AT247" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="252" spans="45:45">
-      <c r="AS252" t="s">
+    <row r="248" spans="46:46">
+      <c r="AT248" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="253" spans="45:45">
-      <c r="AS253" t="s">
+    <row r="249" spans="46:46">
+      <c r="AT249" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="254" spans="45:45">
-      <c r="AS254" t="s">
+    <row r="250" spans="46:46">
+      <c r="AT250" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="255" spans="45:45">
-      <c r="AS255" t="s">
+    <row r="251" spans="46:46">
+      <c r="AT251" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="256" spans="45:45">
-      <c r="AS256" t="s">
+    <row r="252" spans="46:46">
+      <c r="AT252" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="257" spans="45:45">
-      <c r="AS257" t="s">
+    <row r="253" spans="46:46">
+      <c r="AT253" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="258" spans="45:45">
-      <c r="AS258" t="s">
+    <row r="254" spans="46:46">
+      <c r="AT254" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="259" spans="45:45">
-      <c r="AS259" t="s">
+    <row r="255" spans="46:46">
+      <c r="AT255" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="260" spans="45:45">
-      <c r="AS260" t="s">
+    <row r="256" spans="46:46">
+      <c r="AT256" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="261" spans="45:45">
-      <c r="AS261" t="s">
+    <row r="257" spans="46:46">
+      <c r="AT257" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="262" spans="45:45">
-      <c r="AS262" t="s">
+    <row r="258" spans="46:46">
+      <c r="AT258" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="263" spans="45:45">
-      <c r="AS263" t="s">
+    <row r="259" spans="46:46">
+      <c r="AT259" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="264" spans="45:45">
-      <c r="AS264" t="s">
+    <row r="260" spans="46:46">
+      <c r="AT260" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="265" spans="45:45">
-      <c r="AS265" t="s">
+    <row r="261" spans="46:46">
+      <c r="AT261" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="266" spans="45:45">
-      <c r="AS266" t="s">
+    <row r="262" spans="46:46">
+      <c r="AT262" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="267" spans="45:45">
-      <c r="AS267" t="s">
+    <row r="263" spans="46:46">
+      <c r="AT263" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="268" spans="45:45">
-      <c r="AS268" t="s">
+    <row r="264" spans="46:46">
+      <c r="AT264" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="269" spans="45:45">
-      <c r="AS269" t="s">
+    <row r="265" spans="46:46">
+      <c r="AT265" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="270" spans="45:45">
-      <c r="AS270" t="s">
+    <row r="266" spans="46:46">
+      <c r="AT266" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="271" spans="45:45">
-      <c r="AS271" t="s">
+    <row r="267" spans="46:46">
+      <c r="AT267" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="272" spans="45:45">
-      <c r="AS272" t="s">
+    <row r="268" spans="46:46">
+      <c r="AT268" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="273" spans="45:45">
-      <c r="AS273" t="s">
+    <row r="269" spans="46:46">
+      <c r="AT269" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="274" spans="45:45">
-      <c r="AS274" t="s">
+    <row r="270" spans="46:46">
+      <c r="AT270" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="275" spans="45:45">
-      <c r="AS275" t="s">
+    <row r="271" spans="46:46">
+      <c r="AT271" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="276" spans="45:45">
-      <c r="AS276" t="s">
+    <row r="272" spans="46:46">
+      <c r="AT272" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="277" spans="45:45">
-      <c r="AS277" t="s">
+    <row r="273" spans="46:46">
+      <c r="AT273" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="278" spans="45:45">
-      <c r="AS278" t="s">
+    <row r="274" spans="46:46">
+      <c r="AT274" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="279" spans="45:45">
-      <c r="AS279" t="s">
+    <row r="275" spans="46:46">
+      <c r="AT275" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="280" spans="45:45">
-      <c r="AS280" t="s">
+    <row r="276" spans="46:46">
+      <c r="AT276" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="281" spans="45:45">
-      <c r="AS281" t="s">
+    <row r="277" spans="46:46">
+      <c r="AT277" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="282" spans="45:45">
-      <c r="AS282" t="s">
+    <row r="278" spans="46:46">
+      <c r="AT278" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="283" spans="45:45">
-      <c r="AS283" t="s">
+    <row r="279" spans="46:46">
+      <c r="AT279" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="284" spans="45:45">
-      <c r="AS284" t="s">
+    <row r="280" spans="46:46">
+      <c r="AT280" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="285" spans="45:45">
-      <c r="AS285" t="s">
+    <row r="281" spans="46:46">
+      <c r="AT281" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="286" spans="45:45">
-      <c r="AS286" t="s">
+    <row r="282" spans="46:46">
+      <c r="AT282" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="287" spans="45:45">
-      <c r="AS287" t="s">
+    <row r="283" spans="46:46">
+      <c r="AT283" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="288" spans="45:45">
-      <c r="AS288" t="s">
+    <row r="284" spans="46:46">
+      <c r="AT284" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="289" spans="45:45">
-      <c r="AS289" t="s">
+    <row r="285" spans="46:46">
+      <c r="AT285" t="s">
         <v>652</v>
+      </c>
+    </row>
+    <row r="286" spans="46:46">
+      <c r="AT286" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="287" spans="46:46">
+      <c r="AT287" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="288" spans="46:46">
+      <c r="AT288" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="289" spans="46:46">
+      <c r="AT289" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="290" spans="46:46">
+      <c r="AT290" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="291" spans="46:46">
+      <c r="AT291" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="292" spans="46:46">
+      <c r="AT292" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="293" spans="46:46">
+      <c r="AT293" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="294" spans="46:46">
+      <c r="AT294" t="s">
+        <v>661</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000047/metadata_template_ERC000047.xlsx
+++ b/templates/ERC000047/metadata_template_ERC000047.xlsx
@@ -17,17 +17,17 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="assemblyquality">'cv_sample'!$AE$1:$AE$3</definedName>
-    <definedName name="contaminationscreeninginput">'cv_sample'!$Y$1:$Y$2</definedName>
+    <definedName name="assemblyquality">'cv_sample'!$AF$1:$AF$3</definedName>
+    <definedName name="contaminationscreeninginput">'cv_sample'!$Z$1:$Z$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AT$1:$AT$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="reassemblypostbinning">'cv_sample'!$AC$1:$AC$2</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$F$1:$F$7</definedName>
+    <definedName name="reassemblypostbinning">'cv_sample'!$AD$1:$AD$2</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$G$1:$G$7</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="698">
   <si>
     <t>alias</t>
   </si>
@@ -851,6 +851,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3646,13 +3652,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BJ2"/>
+  <dimension ref="A1:BK2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62">
+    <row r="1" spans="1:63">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3669,7 +3675,7 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>283</v>
@@ -3705,7 +3711,7 @@
         <v>303</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>309</v>
@@ -3726,7 +3732,7 @@
         <v>319</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>325</v>
@@ -3744,7 +3750,7 @@
         <v>333</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>340</v>
@@ -3789,7 +3795,7 @@
         <v>366</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>662</v>
+        <v>368</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>664</v>
@@ -3839,8 +3845,11 @@
       <c r="BJ1" s="1" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="2" spans="1:62" ht="150" customHeight="1">
+      <c r="BK1" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -3857,7 +3866,7 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>284</v>
@@ -3893,7 +3902,7 @@
         <v>304</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>310</v>
@@ -3914,7 +3923,7 @@
         <v>320</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>326</v>
@@ -3932,7 +3941,7 @@
         <v>334</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>341</v>
@@ -3977,7 +3986,7 @@
         <v>367</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>663</v>
+        <v>369</v>
       </c>
       <c r="AU2" s="2" t="s">
         <v>665</v>
@@ -4027,25 +4036,28 @@
       <c r="BJ2" s="2" t="s">
         <v>695</v>
       </c>
+      <c r="BK2" s="2" t="s">
+        <v>697</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
       <formula1>contaminationscreeninginput</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>reassemblypostbinning</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
       <formula1>assemblyquality</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -4055,1525 +4067,1525 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:AT294"/>
+  <dimension ref="G1:AU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:46">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
-      <c r="R1" t="s">
-        <v>305</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>321</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>335</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="2" spans="6:46">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
-      <c r="R2" t="s">
-        <v>306</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>336</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="3" spans="6:46">
-      <c r="F3" t="s">
+    <row r="1" spans="7:47">
+      <c r="G1" t="s">
         <v>276</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="S1" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>307</v>
+      </c>
+      <c r="AF1" t="s">
         <v>337</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AU1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="4" spans="6:46">
-      <c r="F4" t="s">
+    <row r="2" spans="7:47">
+      <c r="G2" t="s">
         <v>277</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="S2" t="s">
+        <v>308</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>338</v>
+      </c>
+      <c r="AU2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="5" spans="6:46">
-      <c r="F5" t="s">
+    <row r="3" spans="7:47">
+      <c r="G3" t="s">
         <v>278</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AF3" t="s">
+        <v>339</v>
+      </c>
+      <c r="AU3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="6" spans="6:46">
-      <c r="F6" t="s">
+    <row r="4" spans="7:47">
+      <c r="G4" t="s">
         <v>279</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="7" spans="6:46">
-      <c r="F7" t="s">
+    <row r="5" spans="7:47">
+      <c r="G5" t="s">
         <v>280</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AU5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="8" spans="6:46">
-      <c r="AT8" t="s">
+    <row r="6" spans="7:47">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="AU6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="6:46">
-      <c r="AT9" t="s">
+    <row r="7" spans="7:47">
+      <c r="G7" t="s">
+        <v>282</v>
+      </c>
+      <c r="AU7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="6:46">
-      <c r="AT10" t="s">
+    <row r="8" spans="7:47">
+      <c r="AU8" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="11" spans="6:46">
-      <c r="AT11" t="s">
+    <row r="9" spans="7:47">
+      <c r="AU9" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="6:46">
-      <c r="AT12" t="s">
+    <row r="10" spans="7:47">
+      <c r="AU10" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="13" spans="6:46">
-      <c r="AT13" t="s">
+    <row r="11" spans="7:47">
+      <c r="AU11" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="6:46">
-      <c r="AT14" t="s">
+    <row r="12" spans="7:47">
+      <c r="AU12" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="15" spans="6:46">
-      <c r="AT15" t="s">
+    <row r="13" spans="7:47">
+      <c r="AU13" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="16" spans="6:46">
-      <c r="AT16" t="s">
+    <row r="14" spans="7:47">
+      <c r="AU14" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="17" spans="46:46">
-      <c r="AT17" t="s">
+    <row r="15" spans="7:47">
+      <c r="AU15" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="18" spans="46:46">
-      <c r="AT18" t="s">
+    <row r="16" spans="7:47">
+      <c r="AU16" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="19" spans="46:46">
-      <c r="AT19" t="s">
+    <row r="17" spans="47:47">
+      <c r="AU17" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="20" spans="46:46">
-      <c r="AT20" t="s">
+    <row r="18" spans="47:47">
+      <c r="AU18" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="21" spans="46:46">
-      <c r="AT21" t="s">
+    <row r="19" spans="47:47">
+      <c r="AU19" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="22" spans="46:46">
-      <c r="AT22" t="s">
+    <row r="20" spans="47:47">
+      <c r="AU20" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="46:46">
-      <c r="AT23" t="s">
+    <row r="21" spans="47:47">
+      <c r="AU21" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="24" spans="46:46">
-      <c r="AT24" t="s">
+    <row r="22" spans="47:47">
+      <c r="AU22" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="25" spans="46:46">
-      <c r="AT25" t="s">
+    <row r="23" spans="47:47">
+      <c r="AU23" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="26" spans="46:46">
-      <c r="AT26" t="s">
+    <row r="24" spans="47:47">
+      <c r="AU24" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="27" spans="46:46">
-      <c r="AT27" t="s">
+    <row r="25" spans="47:47">
+      <c r="AU25" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="28" spans="46:46">
-      <c r="AT28" t="s">
+    <row r="26" spans="47:47">
+      <c r="AU26" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="46:46">
-      <c r="AT29" t="s">
+    <row r="27" spans="47:47">
+      <c r="AU27" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="30" spans="46:46">
-      <c r="AT30" t="s">
+    <row r="28" spans="47:47">
+      <c r="AU28" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="31" spans="46:46">
-      <c r="AT31" t="s">
+    <row r="29" spans="47:47">
+      <c r="AU29" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="32" spans="46:46">
-      <c r="AT32" t="s">
+    <row r="30" spans="47:47">
+      <c r="AU30" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="33" spans="46:46">
-      <c r="AT33" t="s">
+    <row r="31" spans="47:47">
+      <c r="AU31" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="46:46">
-      <c r="AT34" t="s">
+    <row r="32" spans="47:47">
+      <c r="AU32" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="35" spans="46:46">
-      <c r="AT35" t="s">
+    <row r="33" spans="47:47">
+      <c r="AU33" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="36" spans="46:46">
-      <c r="AT36" t="s">
+    <row r="34" spans="47:47">
+      <c r="AU34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="37" spans="46:46">
-      <c r="AT37" t="s">
+    <row r="35" spans="47:47">
+      <c r="AU35" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="38" spans="46:46">
-      <c r="AT38" t="s">
+    <row r="36" spans="47:47">
+      <c r="AU36" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="39" spans="46:46">
-      <c r="AT39" t="s">
+    <row r="37" spans="47:47">
+      <c r="AU37" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="46:46">
-      <c r="AT40" t="s">
+    <row r="38" spans="47:47">
+      <c r="AU38" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="41" spans="46:46">
-      <c r="AT41" t="s">
+    <row r="39" spans="47:47">
+      <c r="AU39" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="42" spans="46:46">
-      <c r="AT42" t="s">
+    <row r="40" spans="47:47">
+      <c r="AU40" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="43" spans="46:46">
-      <c r="AT43" t="s">
+    <row r="41" spans="47:47">
+      <c r="AU41" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="44" spans="46:46">
-      <c r="AT44" t="s">
+    <row r="42" spans="47:47">
+      <c r="AU42" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="45" spans="46:46">
-      <c r="AT45" t="s">
+    <row r="43" spans="47:47">
+      <c r="AU43" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="46" spans="46:46">
-      <c r="AT46" t="s">
+    <row r="44" spans="47:47">
+      <c r="AU44" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="47" spans="46:46">
-      <c r="AT47" t="s">
+    <row r="45" spans="47:47">
+      <c r="AU45" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="48" spans="46:46">
-      <c r="AT48" t="s">
+    <row r="46" spans="47:47">
+      <c r="AU46" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="49" spans="46:46">
-      <c r="AT49" t="s">
+    <row r="47" spans="47:47">
+      <c r="AU47" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="50" spans="46:46">
-      <c r="AT50" t="s">
+    <row r="48" spans="47:47">
+      <c r="AU48" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="51" spans="46:46">
-      <c r="AT51" t="s">
+    <row r="49" spans="47:47">
+      <c r="AU49" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="52" spans="46:46">
-      <c r="AT52" t="s">
+    <row r="50" spans="47:47">
+      <c r="AU50" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="53" spans="46:46">
-      <c r="AT53" t="s">
+    <row r="51" spans="47:47">
+      <c r="AU51" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="54" spans="46:46">
-      <c r="AT54" t="s">
+    <row r="52" spans="47:47">
+      <c r="AU52" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="55" spans="46:46">
-      <c r="AT55" t="s">
+    <row r="53" spans="47:47">
+      <c r="AU53" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="56" spans="46:46">
-      <c r="AT56" t="s">
+    <row r="54" spans="47:47">
+      <c r="AU54" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="57" spans="46:46">
-      <c r="AT57" t="s">
+    <row r="55" spans="47:47">
+      <c r="AU55" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="58" spans="46:46">
-      <c r="AT58" t="s">
+    <row r="56" spans="47:47">
+      <c r="AU56" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="59" spans="46:46">
-      <c r="AT59" t="s">
+    <row r="57" spans="47:47">
+      <c r="AU57" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="60" spans="46:46">
-      <c r="AT60" t="s">
+    <row r="58" spans="47:47">
+      <c r="AU58" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="61" spans="46:46">
-      <c r="AT61" t="s">
+    <row r="59" spans="47:47">
+      <c r="AU59" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="62" spans="46:46">
-      <c r="AT62" t="s">
+    <row r="60" spans="47:47">
+      <c r="AU60" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="63" spans="46:46">
-      <c r="AT63" t="s">
+    <row r="61" spans="47:47">
+      <c r="AU61" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="64" spans="46:46">
-      <c r="AT64" t="s">
+    <row r="62" spans="47:47">
+      <c r="AU62" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="65" spans="46:46">
-      <c r="AT65" t="s">
+    <row r="63" spans="47:47">
+      <c r="AU63" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="66" spans="46:46">
-      <c r="AT66" t="s">
+    <row r="64" spans="47:47">
+      <c r="AU64" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="67" spans="46:46">
-      <c r="AT67" t="s">
+    <row r="65" spans="47:47">
+      <c r="AU65" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="68" spans="46:46">
-      <c r="AT68" t="s">
+    <row r="66" spans="47:47">
+      <c r="AU66" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="69" spans="46:46">
-      <c r="AT69" t="s">
+    <row r="67" spans="47:47">
+      <c r="AU67" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="70" spans="46:46">
-      <c r="AT70" t="s">
+    <row r="68" spans="47:47">
+      <c r="AU68" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="71" spans="46:46">
-      <c r="AT71" t="s">
+    <row r="69" spans="47:47">
+      <c r="AU69" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="72" spans="46:46">
-      <c r="AT72" t="s">
+    <row r="70" spans="47:47">
+      <c r="AU70" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="73" spans="46:46">
-      <c r="AT73" t="s">
+    <row r="71" spans="47:47">
+      <c r="AU71" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="74" spans="46:46">
-      <c r="AT74" t="s">
+    <row r="72" spans="47:47">
+      <c r="AU72" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="75" spans="46:46">
-      <c r="AT75" t="s">
+    <row r="73" spans="47:47">
+      <c r="AU73" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="76" spans="46:46">
-      <c r="AT76" t="s">
+    <row r="74" spans="47:47">
+      <c r="AU74" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="77" spans="46:46">
-      <c r="AT77" t="s">
+    <row r="75" spans="47:47">
+      <c r="AU75" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="78" spans="46:46">
-      <c r="AT78" t="s">
+    <row r="76" spans="47:47">
+      <c r="AU76" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="79" spans="46:46">
-      <c r="AT79" t="s">
+    <row r="77" spans="47:47">
+      <c r="AU77" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="80" spans="46:46">
-      <c r="AT80" t="s">
+    <row r="78" spans="47:47">
+      <c r="AU78" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="81" spans="46:46">
-      <c r="AT81" t="s">
+    <row r="79" spans="47:47">
+      <c r="AU79" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="82" spans="46:46">
-      <c r="AT82" t="s">
+    <row r="80" spans="47:47">
+      <c r="AU80" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="83" spans="46:46">
-      <c r="AT83" t="s">
+    <row r="81" spans="47:47">
+      <c r="AU81" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="84" spans="46:46">
-      <c r="AT84" t="s">
+    <row r="82" spans="47:47">
+      <c r="AU82" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="85" spans="46:46">
-      <c r="AT85" t="s">
+    <row r="83" spans="47:47">
+      <c r="AU83" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="86" spans="46:46">
-      <c r="AT86" t="s">
+    <row r="84" spans="47:47">
+      <c r="AU84" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="87" spans="46:46">
-      <c r="AT87" t="s">
+    <row r="85" spans="47:47">
+      <c r="AU85" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="88" spans="46:46">
-      <c r="AT88" t="s">
+    <row r="86" spans="47:47">
+      <c r="AU86" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="89" spans="46:46">
-      <c r="AT89" t="s">
+    <row r="87" spans="47:47">
+      <c r="AU87" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="90" spans="46:46">
-      <c r="AT90" t="s">
+    <row r="88" spans="47:47">
+      <c r="AU88" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="91" spans="46:46">
-      <c r="AT91" t="s">
+    <row r="89" spans="47:47">
+      <c r="AU89" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="92" spans="46:46">
-      <c r="AT92" t="s">
+    <row r="90" spans="47:47">
+      <c r="AU90" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="93" spans="46:46">
-      <c r="AT93" t="s">
+    <row r="91" spans="47:47">
+      <c r="AU91" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="94" spans="46:46">
-      <c r="AT94" t="s">
+    <row r="92" spans="47:47">
+      <c r="AU92" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="95" spans="46:46">
-      <c r="AT95" t="s">
+    <row r="93" spans="47:47">
+      <c r="AU93" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="96" spans="46:46">
-      <c r="AT96" t="s">
+    <row r="94" spans="47:47">
+      <c r="AU94" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="97" spans="46:46">
-      <c r="AT97" t="s">
+    <row r="95" spans="47:47">
+      <c r="AU95" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="98" spans="46:46">
-      <c r="AT98" t="s">
+    <row r="96" spans="47:47">
+      <c r="AU96" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="99" spans="46:46">
-      <c r="AT99" t="s">
+    <row r="97" spans="47:47">
+      <c r="AU97" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="100" spans="46:46">
-      <c r="AT100" t="s">
+    <row r="98" spans="47:47">
+      <c r="AU98" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="101" spans="46:46">
-      <c r="AT101" t="s">
+    <row r="99" spans="47:47">
+      <c r="AU99" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="102" spans="46:46">
-      <c r="AT102" t="s">
+    <row r="100" spans="47:47">
+      <c r="AU100" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="103" spans="46:46">
-      <c r="AT103" t="s">
+    <row r="101" spans="47:47">
+      <c r="AU101" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="104" spans="46:46">
-      <c r="AT104" t="s">
+    <row r="102" spans="47:47">
+      <c r="AU102" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="105" spans="46:46">
-      <c r="AT105" t="s">
+    <row r="103" spans="47:47">
+      <c r="AU103" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="106" spans="46:46">
-      <c r="AT106" t="s">
+    <row r="104" spans="47:47">
+      <c r="AU104" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="107" spans="46:46">
-      <c r="AT107" t="s">
+    <row r="105" spans="47:47">
+      <c r="AU105" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="108" spans="46:46">
-      <c r="AT108" t="s">
+    <row r="106" spans="47:47">
+      <c r="AU106" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="109" spans="46:46">
-      <c r="AT109" t="s">
+    <row r="107" spans="47:47">
+      <c r="AU107" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="110" spans="46:46">
-      <c r="AT110" t="s">
+    <row r="108" spans="47:47">
+      <c r="AU108" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="111" spans="46:46">
-      <c r="AT111" t="s">
+    <row r="109" spans="47:47">
+      <c r="AU109" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="112" spans="46:46">
-      <c r="AT112" t="s">
+    <row r="110" spans="47:47">
+      <c r="AU110" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="113" spans="46:46">
-      <c r="AT113" t="s">
+    <row r="111" spans="47:47">
+      <c r="AU111" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="114" spans="46:46">
-      <c r="AT114" t="s">
+    <row r="112" spans="47:47">
+      <c r="AU112" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="115" spans="46:46">
-      <c r="AT115" t="s">
+    <row r="113" spans="47:47">
+      <c r="AU113" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="116" spans="46:46">
-      <c r="AT116" t="s">
+    <row r="114" spans="47:47">
+      <c r="AU114" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="117" spans="46:46">
-      <c r="AT117" t="s">
+    <row r="115" spans="47:47">
+      <c r="AU115" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="118" spans="46:46">
-      <c r="AT118" t="s">
+    <row r="116" spans="47:47">
+      <c r="AU116" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="119" spans="46:46">
-      <c r="AT119" t="s">
+    <row r="117" spans="47:47">
+      <c r="AU117" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="120" spans="46:46">
-      <c r="AT120" t="s">
+    <row r="118" spans="47:47">
+      <c r="AU118" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="121" spans="46:46">
-      <c r="AT121" t="s">
+    <row r="119" spans="47:47">
+      <c r="AU119" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="122" spans="46:46">
-      <c r="AT122" t="s">
+    <row r="120" spans="47:47">
+      <c r="AU120" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="123" spans="46:46">
-      <c r="AT123" t="s">
+    <row r="121" spans="47:47">
+      <c r="AU121" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="124" spans="46:46">
-      <c r="AT124" t="s">
+    <row r="122" spans="47:47">
+      <c r="AU122" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="125" spans="46:46">
-      <c r="AT125" t="s">
+    <row r="123" spans="47:47">
+      <c r="AU123" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="126" spans="46:46">
-      <c r="AT126" t="s">
+    <row r="124" spans="47:47">
+      <c r="AU124" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="127" spans="46:46">
-      <c r="AT127" t="s">
+    <row r="125" spans="47:47">
+      <c r="AU125" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="128" spans="46:46">
-      <c r="AT128" t="s">
+    <row r="126" spans="47:47">
+      <c r="AU126" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="129" spans="46:46">
-      <c r="AT129" t="s">
+    <row r="127" spans="47:47">
+      <c r="AU127" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="130" spans="46:46">
-      <c r="AT130" t="s">
+    <row r="128" spans="47:47">
+      <c r="AU128" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="131" spans="46:46">
-      <c r="AT131" t="s">
+    <row r="129" spans="47:47">
+      <c r="AU129" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="132" spans="46:46">
-      <c r="AT132" t="s">
+    <row r="130" spans="47:47">
+      <c r="AU130" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="133" spans="46:46">
-      <c r="AT133" t="s">
+    <row r="131" spans="47:47">
+      <c r="AU131" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="134" spans="46:46">
-      <c r="AT134" t="s">
+    <row r="132" spans="47:47">
+      <c r="AU132" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="135" spans="46:46">
-      <c r="AT135" t="s">
+    <row r="133" spans="47:47">
+      <c r="AU133" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="136" spans="46:46">
-      <c r="AT136" t="s">
+    <row r="134" spans="47:47">
+      <c r="AU134" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="137" spans="46:46">
-      <c r="AT137" t="s">
+    <row r="135" spans="47:47">
+      <c r="AU135" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="138" spans="46:46">
-      <c r="AT138" t="s">
+    <row r="136" spans="47:47">
+      <c r="AU136" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="139" spans="46:46">
-      <c r="AT139" t="s">
+    <row r="137" spans="47:47">
+      <c r="AU137" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="140" spans="46:46">
-      <c r="AT140" t="s">
+    <row r="138" spans="47:47">
+      <c r="AU138" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="141" spans="46:46">
-      <c r="AT141" t="s">
+    <row r="139" spans="47:47">
+      <c r="AU139" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="142" spans="46:46">
-      <c r="AT142" t="s">
+    <row r="140" spans="47:47">
+      <c r="AU140" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="143" spans="46:46">
-      <c r="AT143" t="s">
+    <row r="141" spans="47:47">
+      <c r="AU141" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="144" spans="46:46">
-      <c r="AT144" t="s">
+    <row r="142" spans="47:47">
+      <c r="AU142" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="145" spans="46:46">
-      <c r="AT145" t="s">
+    <row r="143" spans="47:47">
+      <c r="AU143" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="146" spans="46:46">
-      <c r="AT146" t="s">
+    <row r="144" spans="47:47">
+      <c r="AU144" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="147" spans="46:46">
-      <c r="AT147" t="s">
+    <row r="145" spans="47:47">
+      <c r="AU145" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="148" spans="46:46">
-      <c r="AT148" t="s">
+    <row r="146" spans="47:47">
+      <c r="AU146" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="149" spans="46:46">
-      <c r="AT149" t="s">
+    <row r="147" spans="47:47">
+      <c r="AU147" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="150" spans="46:46">
-      <c r="AT150" t="s">
+    <row r="148" spans="47:47">
+      <c r="AU148" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="151" spans="46:46">
-      <c r="AT151" t="s">
+    <row r="149" spans="47:47">
+      <c r="AU149" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="152" spans="46:46">
-      <c r="AT152" t="s">
+    <row r="150" spans="47:47">
+      <c r="AU150" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="153" spans="46:46">
-      <c r="AT153" t="s">
+    <row r="151" spans="47:47">
+      <c r="AU151" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="154" spans="46:46">
-      <c r="AT154" t="s">
+    <row r="152" spans="47:47">
+      <c r="AU152" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="155" spans="46:46">
-      <c r="AT155" t="s">
+    <row r="153" spans="47:47">
+      <c r="AU153" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="156" spans="46:46">
-      <c r="AT156" t="s">
+    <row r="154" spans="47:47">
+      <c r="AU154" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="157" spans="46:46">
-      <c r="AT157" t="s">
+    <row r="155" spans="47:47">
+      <c r="AU155" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="158" spans="46:46">
-      <c r="AT158" t="s">
+    <row r="156" spans="47:47">
+      <c r="AU156" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="159" spans="46:46">
-      <c r="AT159" t="s">
+    <row r="157" spans="47:47">
+      <c r="AU157" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="160" spans="46:46">
-      <c r="AT160" t="s">
+    <row r="158" spans="47:47">
+      <c r="AU158" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="161" spans="46:46">
-      <c r="AT161" t="s">
+    <row r="159" spans="47:47">
+      <c r="AU159" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="162" spans="46:46">
-      <c r="AT162" t="s">
+    <row r="160" spans="47:47">
+      <c r="AU160" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="163" spans="46:46">
-      <c r="AT163" t="s">
+    <row r="161" spans="47:47">
+      <c r="AU161" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="164" spans="46:46">
-      <c r="AT164" t="s">
+    <row r="162" spans="47:47">
+      <c r="AU162" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="165" spans="46:46">
-      <c r="AT165" t="s">
+    <row r="163" spans="47:47">
+      <c r="AU163" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="166" spans="46:46">
-      <c r="AT166" t="s">
+    <row r="164" spans="47:47">
+      <c r="AU164" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="167" spans="46:46">
-      <c r="AT167" t="s">
+    <row r="165" spans="47:47">
+      <c r="AU165" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="168" spans="46:46">
-      <c r="AT168" t="s">
+    <row r="166" spans="47:47">
+      <c r="AU166" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="169" spans="46:46">
-      <c r="AT169" t="s">
+    <row r="167" spans="47:47">
+      <c r="AU167" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="170" spans="46:46">
-      <c r="AT170" t="s">
+    <row r="168" spans="47:47">
+      <c r="AU168" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="171" spans="46:46">
-      <c r="AT171" t="s">
+    <row r="169" spans="47:47">
+      <c r="AU169" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="172" spans="46:46">
-      <c r="AT172" t="s">
+    <row r="170" spans="47:47">
+      <c r="AU170" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="173" spans="46:46">
-      <c r="AT173" t="s">
+    <row r="171" spans="47:47">
+      <c r="AU171" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="174" spans="46:46">
-      <c r="AT174" t="s">
+    <row r="172" spans="47:47">
+      <c r="AU172" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="175" spans="46:46">
-      <c r="AT175" t="s">
+    <row r="173" spans="47:47">
+      <c r="AU173" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="176" spans="46:46">
-      <c r="AT176" t="s">
+    <row r="174" spans="47:47">
+      <c r="AU174" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="177" spans="46:46">
-      <c r="AT177" t="s">
+    <row r="175" spans="47:47">
+      <c r="AU175" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="178" spans="46:46">
-      <c r="AT178" t="s">
+    <row r="176" spans="47:47">
+      <c r="AU176" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="179" spans="46:46">
-      <c r="AT179" t="s">
+    <row r="177" spans="47:47">
+      <c r="AU177" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="180" spans="46:46">
-      <c r="AT180" t="s">
+    <row r="178" spans="47:47">
+      <c r="AU178" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="181" spans="46:46">
-      <c r="AT181" t="s">
+    <row r="179" spans="47:47">
+      <c r="AU179" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="182" spans="46:46">
-      <c r="AT182" t="s">
+    <row r="180" spans="47:47">
+      <c r="AU180" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="183" spans="46:46">
-      <c r="AT183" t="s">
+    <row r="181" spans="47:47">
+      <c r="AU181" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="184" spans="46:46">
-      <c r="AT184" t="s">
+    <row r="182" spans="47:47">
+      <c r="AU182" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="185" spans="46:46">
-      <c r="AT185" t="s">
+    <row r="183" spans="47:47">
+      <c r="AU183" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="186" spans="46:46">
-      <c r="AT186" t="s">
+    <row r="184" spans="47:47">
+      <c r="AU184" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="187" spans="46:46">
-      <c r="AT187" t="s">
+    <row r="185" spans="47:47">
+      <c r="AU185" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="188" spans="46:46">
-      <c r="AT188" t="s">
+    <row r="186" spans="47:47">
+      <c r="AU186" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="189" spans="46:46">
-      <c r="AT189" t="s">
+    <row r="187" spans="47:47">
+      <c r="AU187" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="190" spans="46:46">
-      <c r="AT190" t="s">
+    <row r="188" spans="47:47">
+      <c r="AU188" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="191" spans="46:46">
-      <c r="AT191" t="s">
+    <row r="189" spans="47:47">
+      <c r="AU189" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="192" spans="46:46">
-      <c r="AT192" t="s">
+    <row r="190" spans="47:47">
+      <c r="AU190" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="193" spans="46:46">
-      <c r="AT193" t="s">
+    <row r="191" spans="47:47">
+      <c r="AU191" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="194" spans="46:46">
-      <c r="AT194" t="s">
+    <row r="192" spans="47:47">
+      <c r="AU192" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="195" spans="46:46">
-      <c r="AT195" t="s">
+    <row r="193" spans="47:47">
+      <c r="AU193" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="196" spans="46:46">
-      <c r="AT196" t="s">
+    <row r="194" spans="47:47">
+      <c r="AU194" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="197" spans="46:46">
-      <c r="AT197" t="s">
+    <row r="195" spans="47:47">
+      <c r="AU195" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="198" spans="46:46">
-      <c r="AT198" t="s">
+    <row r="196" spans="47:47">
+      <c r="AU196" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="199" spans="46:46">
-      <c r="AT199" t="s">
+    <row r="197" spans="47:47">
+      <c r="AU197" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="200" spans="46:46">
-      <c r="AT200" t="s">
+    <row r="198" spans="47:47">
+      <c r="AU198" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="201" spans="46:46">
-      <c r="AT201" t="s">
+    <row r="199" spans="47:47">
+      <c r="AU199" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="202" spans="46:46">
-      <c r="AT202" t="s">
+    <row r="200" spans="47:47">
+      <c r="AU200" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="203" spans="46:46">
-      <c r="AT203" t="s">
+    <row r="201" spans="47:47">
+      <c r="AU201" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="204" spans="46:46">
-      <c r="AT204" t="s">
+    <row r="202" spans="47:47">
+      <c r="AU202" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="205" spans="46:46">
-      <c r="AT205" t="s">
+    <row r="203" spans="47:47">
+      <c r="AU203" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="206" spans="46:46">
-      <c r="AT206" t="s">
+    <row r="204" spans="47:47">
+      <c r="AU204" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="207" spans="46:46">
-      <c r="AT207" t="s">
+    <row r="205" spans="47:47">
+      <c r="AU205" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="208" spans="46:46">
-      <c r="AT208" t="s">
+    <row r="206" spans="47:47">
+      <c r="AU206" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="209" spans="46:46">
-      <c r="AT209" t="s">
+    <row r="207" spans="47:47">
+      <c r="AU207" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="210" spans="46:46">
-      <c r="AT210" t="s">
+    <row r="208" spans="47:47">
+      <c r="AU208" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="211" spans="46:46">
-      <c r="AT211" t="s">
+    <row r="209" spans="47:47">
+      <c r="AU209" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="212" spans="46:46">
-      <c r="AT212" t="s">
+    <row r="210" spans="47:47">
+      <c r="AU210" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="213" spans="46:46">
-      <c r="AT213" t="s">
+    <row r="211" spans="47:47">
+      <c r="AU211" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="214" spans="46:46">
-      <c r="AT214" t="s">
+    <row r="212" spans="47:47">
+      <c r="AU212" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="215" spans="46:46">
-      <c r="AT215" t="s">
+    <row r="213" spans="47:47">
+      <c r="AU213" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="216" spans="46:46">
-      <c r="AT216" t="s">
+    <row r="214" spans="47:47">
+      <c r="AU214" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="217" spans="46:46">
-      <c r="AT217" t="s">
+    <row r="215" spans="47:47">
+      <c r="AU215" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="218" spans="46:46">
-      <c r="AT218" t="s">
+    <row r="216" spans="47:47">
+      <c r="AU216" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="219" spans="46:46">
-      <c r="AT219" t="s">
+    <row r="217" spans="47:47">
+      <c r="AU217" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="220" spans="46:46">
-      <c r="AT220" t="s">
+    <row r="218" spans="47:47">
+      <c r="AU218" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="221" spans="46:46">
-      <c r="AT221" t="s">
+    <row r="219" spans="47:47">
+      <c r="AU219" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="222" spans="46:46">
-      <c r="AT222" t="s">
+    <row r="220" spans="47:47">
+      <c r="AU220" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="223" spans="46:46">
-      <c r="AT223" t="s">
+    <row r="221" spans="47:47">
+      <c r="AU221" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="224" spans="46:46">
-      <c r="AT224" t="s">
+    <row r="222" spans="47:47">
+      <c r="AU222" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="225" spans="46:46">
-      <c r="AT225" t="s">
+    <row r="223" spans="47:47">
+      <c r="AU223" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="226" spans="46:46">
-      <c r="AT226" t="s">
+    <row r="224" spans="47:47">
+      <c r="AU224" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="227" spans="46:46">
-      <c r="AT227" t="s">
+    <row r="225" spans="47:47">
+      <c r="AU225" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="228" spans="46:46">
-      <c r="AT228" t="s">
+    <row r="226" spans="47:47">
+      <c r="AU226" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="229" spans="46:46">
-      <c r="AT229" t="s">
+    <row r="227" spans="47:47">
+      <c r="AU227" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="230" spans="46:46">
-      <c r="AT230" t="s">
+    <row r="228" spans="47:47">
+      <c r="AU228" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="231" spans="46:46">
-      <c r="AT231" t="s">
+    <row r="229" spans="47:47">
+      <c r="AU229" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="232" spans="46:46">
-      <c r="AT232" t="s">
+    <row r="230" spans="47:47">
+      <c r="AU230" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="233" spans="46:46">
-      <c r="AT233" t="s">
+    <row r="231" spans="47:47">
+      <c r="AU231" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="234" spans="46:46">
-      <c r="AT234" t="s">
+    <row r="232" spans="47:47">
+      <c r="AU232" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="235" spans="46:46">
-      <c r="AT235" t="s">
+    <row r="233" spans="47:47">
+      <c r="AU233" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="236" spans="46:46">
-      <c r="AT236" t="s">
+    <row r="234" spans="47:47">
+      <c r="AU234" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="237" spans="46:46">
-      <c r="AT237" t="s">
+    <row r="235" spans="47:47">
+      <c r="AU235" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="238" spans="46:46">
-      <c r="AT238" t="s">
+    <row r="236" spans="47:47">
+      <c r="AU236" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="239" spans="46:46">
-      <c r="AT239" t="s">
+    <row r="237" spans="47:47">
+      <c r="AU237" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="240" spans="46:46">
-      <c r="AT240" t="s">
+    <row r="238" spans="47:47">
+      <c r="AU238" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="241" spans="46:46">
-      <c r="AT241" t="s">
+    <row r="239" spans="47:47">
+      <c r="AU239" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="242" spans="46:46">
-      <c r="AT242" t="s">
+    <row r="240" spans="47:47">
+      <c r="AU240" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="243" spans="46:46">
-      <c r="AT243" t="s">
+    <row r="241" spans="47:47">
+      <c r="AU241" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="244" spans="46:46">
-      <c r="AT244" t="s">
+    <row r="242" spans="47:47">
+      <c r="AU242" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="245" spans="46:46">
-      <c r="AT245" t="s">
+    <row r="243" spans="47:47">
+      <c r="AU243" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="246" spans="46:46">
-      <c r="AT246" t="s">
+    <row r="244" spans="47:47">
+      <c r="AU244" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="247" spans="46:46">
-      <c r="AT247" t="s">
+    <row r="245" spans="47:47">
+      <c r="AU245" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="248" spans="46:46">
-      <c r="AT248" t="s">
+    <row r="246" spans="47:47">
+      <c r="AU246" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="249" spans="46:46">
-      <c r="AT249" t="s">
+    <row r="247" spans="47:47">
+      <c r="AU247" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="250" spans="46:46">
-      <c r="AT250" t="s">
+    <row r="248" spans="47:47">
+      <c r="AU248" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="251" spans="46:46">
-      <c r="AT251" t="s">
+    <row r="249" spans="47:47">
+      <c r="AU249" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="252" spans="46:46">
-      <c r="AT252" t="s">
+    <row r="250" spans="47:47">
+      <c r="AU250" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="253" spans="46:46">
-      <c r="AT253" t="s">
+    <row r="251" spans="47:47">
+      <c r="AU251" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="254" spans="46:46">
-      <c r="AT254" t="s">
+    <row r="252" spans="47:47">
+      <c r="AU252" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="255" spans="46:46">
-      <c r="AT255" t="s">
+    <row r="253" spans="47:47">
+      <c r="AU253" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="256" spans="46:46">
-      <c r="AT256" t="s">
+    <row r="254" spans="47:47">
+      <c r="AU254" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="257" spans="46:46">
-      <c r="AT257" t="s">
+    <row r="255" spans="47:47">
+      <c r="AU255" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="258" spans="46:46">
-      <c r="AT258" t="s">
+    <row r="256" spans="47:47">
+      <c r="AU256" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="259" spans="46:46">
-      <c r="AT259" t="s">
+    <row r="257" spans="47:47">
+      <c r="AU257" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="260" spans="46:46">
-      <c r="AT260" t="s">
+    <row r="258" spans="47:47">
+      <c r="AU258" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="261" spans="46:46">
-      <c r="AT261" t="s">
+    <row r="259" spans="47:47">
+      <c r="AU259" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="262" spans="46:46">
-      <c r="AT262" t="s">
+    <row r="260" spans="47:47">
+      <c r="AU260" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="263" spans="46:46">
-      <c r="AT263" t="s">
+    <row r="261" spans="47:47">
+      <c r="AU261" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="264" spans="46:46">
-      <c r="AT264" t="s">
+    <row r="262" spans="47:47">
+      <c r="AU262" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="265" spans="46:46">
-      <c r="AT265" t="s">
+    <row r="263" spans="47:47">
+      <c r="AU263" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="266" spans="46:46">
-      <c r="AT266" t="s">
+    <row r="264" spans="47:47">
+      <c r="AU264" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="267" spans="46:46">
-      <c r="AT267" t="s">
+    <row r="265" spans="47:47">
+      <c r="AU265" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="268" spans="46:46">
-      <c r="AT268" t="s">
+    <row r="266" spans="47:47">
+      <c r="AU266" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="269" spans="46:46">
-      <c r="AT269" t="s">
+    <row r="267" spans="47:47">
+      <c r="AU267" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="270" spans="46:46">
-      <c r="AT270" t="s">
+    <row r="268" spans="47:47">
+      <c r="AU268" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="271" spans="46:46">
-      <c r="AT271" t="s">
+    <row r="269" spans="47:47">
+      <c r="AU269" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="272" spans="46:46">
-      <c r="AT272" t="s">
+    <row r="270" spans="47:47">
+      <c r="AU270" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="273" spans="46:46">
-      <c r="AT273" t="s">
+    <row r="271" spans="47:47">
+      <c r="AU271" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="274" spans="46:46">
-      <c r="AT274" t="s">
+    <row r="272" spans="47:47">
+      <c r="AU272" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="275" spans="46:46">
-      <c r="AT275" t="s">
+    <row r="273" spans="47:47">
+      <c r="AU273" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="276" spans="46:46">
-      <c r="AT276" t="s">
+    <row r="274" spans="47:47">
+      <c r="AU274" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="277" spans="46:46">
-      <c r="AT277" t="s">
+    <row r="275" spans="47:47">
+      <c r="AU275" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="278" spans="46:46">
-      <c r="AT278" t="s">
+    <row r="276" spans="47:47">
+      <c r="AU276" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="279" spans="46:46">
-      <c r="AT279" t="s">
+    <row r="277" spans="47:47">
+      <c r="AU277" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="280" spans="46:46">
-      <c r="AT280" t="s">
+    <row r="278" spans="47:47">
+      <c r="AU278" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="281" spans="46:46">
-      <c r="AT281" t="s">
+    <row r="279" spans="47:47">
+      <c r="AU279" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="282" spans="46:46">
-      <c r="AT282" t="s">
+    <row r="280" spans="47:47">
+      <c r="AU280" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="283" spans="46:46">
-      <c r="AT283" t="s">
+    <row r="281" spans="47:47">
+      <c r="AU281" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="284" spans="46:46">
-      <c r="AT284" t="s">
+    <row r="282" spans="47:47">
+      <c r="AU282" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="285" spans="46:46">
-      <c r="AT285" t="s">
+    <row r="283" spans="47:47">
+      <c r="AU283" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="286" spans="46:46">
-      <c r="AT286" t="s">
+    <row r="284" spans="47:47">
+      <c r="AU284" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="287" spans="46:46">
-      <c r="AT287" t="s">
+    <row r="285" spans="47:47">
+      <c r="AU285" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="288" spans="46:46">
-      <c r="AT288" t="s">
+    <row r="286" spans="47:47">
+      <c r="AU286" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="289" spans="46:46">
-      <c r="AT289" t="s">
+    <row r="287" spans="47:47">
+      <c r="AU287" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="290" spans="46:46">
-      <c r="AT290" t="s">
+    <row r="288" spans="47:47">
+      <c r="AU288" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="291" spans="46:46">
-      <c r="AT291" t="s">
+    <row r="289" spans="47:47">
+      <c r="AU289" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="292" spans="46:46">
-      <c r="AT292" t="s">
+    <row r="290" spans="47:47">
+      <c r="AU290" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="293" spans="46:46">
-      <c r="AT293" t="s">
+    <row r="291" spans="47:47">
+      <c r="AU291" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="294" spans="46:46">
-      <c r="AT294" t="s">
+    <row r="292" spans="47:47">
+      <c r="AU292" t="s">
         <v>661</v>
+      </c>
+    </row>
+    <row r="293" spans="47:47">
+      <c r="AU293" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="294" spans="47:47">
+      <c r="AU294" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000047/metadata_template_ERC000047.xlsx
+++ b/templates/ERC000047/metadata_template_ERC000047.xlsx
@@ -20,12 +20,12 @@
     <definedName name="assemblyquality">'cv_sample'!$AF$1:$AF$3</definedName>
     <definedName name="contaminationscreeninginput">'cv_sample'!$Z$1:$Z$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="reassemblypostbinning">'cv_sample'!$AD$1:$AD$2</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$G$1:$G$7</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="698">
   <si>
     <t>alias</t>
   </si>
@@ -451,6 +451,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1354,9 +1360,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1375,6 +1378,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1576,6 +1582,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1585,9 +1594,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1627,7 +1633,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1696,6 +1702,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1771,6 +1780,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1792,6 +1804,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1837,6 +1852,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1849,6 +1867,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1858,9 +1879,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1885,6 +1903,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1945,10 +1966,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2634,10 +2655,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2678,10 +2699,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2708,7 +2729,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2725,7 +2746,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2742,7 +2763,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2759,7 +2780,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2776,7 +2797,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2793,7 +2814,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2810,7 +2831,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2827,7 +2848,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2844,7 +2865,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2861,7 +2882,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2875,7 +2896,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2889,7 +2910,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2903,7 +2924,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2917,7 +2938,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2931,7 +2952,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2945,7 +2966,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2959,7 +2980,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2973,7 +2994,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2983,8 +3004,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2995,7 +3019,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3006,7 +3030,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3017,7 +3041,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3028,7 +3052,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3039,7 +3063,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3050,7 +3074,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3061,7 +3085,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3072,7 +3096,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3083,7 +3107,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3094,7 +3118,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3105,7 +3129,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3116,7 +3140,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3127,7 +3151,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3135,7 +3159,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3143,7 +3167,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3151,7 +3175,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3159,7 +3183,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3167,7 +3191,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3175,7 +3199,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3183,7 +3207,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3191,7 +3215,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3199,7 +3223,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3207,236 +3231,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3458,27 +3487,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3498,122 +3527,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3637,378 +3666,378 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2" spans="1:63" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -4038,1500 +4067,1525 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:AU289"/>
+  <dimension ref="G1:AU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:47">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Z1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AD1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AF1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AU1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="7:47">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Z2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AD2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AF2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AU2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="7:47">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AF3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AU3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="7:47">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AU4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="7:47">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AU5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="7:47">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AU6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="7:47">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AU7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="7:47">
       <c r="AU8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="7:47">
       <c r="AU9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="7:47">
       <c r="AU10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="7:47">
       <c r="AU11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="7:47">
       <c r="AU12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="7:47">
       <c r="AU13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="7:47">
       <c r="AU14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="7:47">
       <c r="AU15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="7:47">
       <c r="AU16" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="47:47">
       <c r="AU17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="47:47">
       <c r="AU18" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="47:47">
       <c r="AU19" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="47:47">
       <c r="AU20" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="47:47">
       <c r="AU21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="47:47">
       <c r="AU22" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="47:47">
       <c r="AU23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" spans="47:47">
       <c r="AU24" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="47:47">
       <c r="AU25" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" spans="47:47">
       <c r="AU26" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="27" spans="47:47">
       <c r="AU27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="47:47">
       <c r="AU28" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="47:47">
       <c r="AU29" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="47:47">
       <c r="AU30" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="31" spans="47:47">
       <c r="AU31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="47:47">
       <c r="AU32" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="47:47">
       <c r="AU33" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="47:47">
       <c r="AU34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="47:47">
       <c r="AU35" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="47:47">
       <c r="AU36" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="47:47">
       <c r="AU37" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="47:47">
       <c r="AU38" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" spans="47:47">
       <c r="AU39" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="47:47">
       <c r="AU40" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="47:47">
       <c r="AU41" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="47:47">
       <c r="AU42" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="47:47">
       <c r="AU43" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="44" spans="47:47">
       <c r="AU44" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="47:47">
       <c r="AU45" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="47:47">
       <c r="AU46" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" spans="47:47">
       <c r="AU47" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" spans="47:47">
       <c r="AU48" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="47:47">
       <c r="AU49" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" spans="47:47">
       <c r="AU50" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="47:47">
       <c r="AU51" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="47:47">
       <c r="AU52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="53" spans="47:47">
       <c r="AU53" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="54" spans="47:47">
       <c r="AU54" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="55" spans="47:47">
       <c r="AU55" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56" spans="47:47">
       <c r="AU56" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" spans="47:47">
       <c r="AU57" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" spans="47:47">
       <c r="AU58" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="59" spans="47:47">
       <c r="AU59" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="60" spans="47:47">
       <c r="AU60" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="61" spans="47:47">
       <c r="AU61" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" spans="47:47">
       <c r="AU62" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" spans="47:47">
       <c r="AU63" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="47:47">
       <c r="AU64" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" spans="47:47">
       <c r="AU65" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66" spans="47:47">
       <c r="AU66" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67" spans="47:47">
       <c r="AU67" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="68" spans="47:47">
       <c r="AU68" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69" spans="47:47">
       <c r="AU69" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="47:47">
       <c r="AU70" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" spans="47:47">
       <c r="AU71" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="47:47">
       <c r="AU72" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="73" spans="47:47">
       <c r="AU73" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="74" spans="47:47">
       <c r="AU74" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75" spans="47:47">
       <c r="AU75" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="76" spans="47:47">
       <c r="AU76" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="47:47">
       <c r="AU77" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="78" spans="47:47">
       <c r="AU78" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="47:47">
       <c r="AU79" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="47:47">
       <c r="AU80" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="47:47">
       <c r="AU81" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="47:47">
       <c r="AU82" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="83" spans="47:47">
       <c r="AU83" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="47:47">
       <c r="AU84" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="85" spans="47:47">
       <c r="AU85" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="86" spans="47:47">
       <c r="AU86" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="87" spans="47:47">
       <c r="AU87" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="88" spans="47:47">
       <c r="AU88" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="89" spans="47:47">
       <c r="AU89" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="90" spans="47:47">
       <c r="AU90" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="91" spans="47:47">
       <c r="AU91" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="92" spans="47:47">
       <c r="AU92" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="93" spans="47:47">
       <c r="AU93" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="94" spans="47:47">
       <c r="AU94" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="95" spans="47:47">
       <c r="AU95" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="96" spans="47:47">
       <c r="AU96" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="97" spans="47:47">
       <c r="AU97" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="98" spans="47:47">
       <c r="AU98" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="99" spans="47:47">
       <c r="AU99" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="100" spans="47:47">
       <c r="AU100" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="101" spans="47:47">
       <c r="AU101" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="102" spans="47:47">
       <c r="AU102" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="103" spans="47:47">
       <c r="AU103" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" spans="47:47">
       <c r="AU104" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="105" spans="47:47">
       <c r="AU105" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="106" spans="47:47">
       <c r="AU106" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="107" spans="47:47">
       <c r="AU107" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="108" spans="47:47">
       <c r="AU108" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="109" spans="47:47">
       <c r="AU109" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="110" spans="47:47">
       <c r="AU110" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="111" spans="47:47">
       <c r="AU111" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="112" spans="47:47">
       <c r="AU112" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="113" spans="47:47">
       <c r="AU113" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="114" spans="47:47">
       <c r="AU114" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="115" spans="47:47">
       <c r="AU115" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="116" spans="47:47">
       <c r="AU116" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="47:47">
       <c r="AU117" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="118" spans="47:47">
       <c r="AU118" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="119" spans="47:47">
       <c r="AU119" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="120" spans="47:47">
       <c r="AU120" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="121" spans="47:47">
       <c r="AU121" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="122" spans="47:47">
       <c r="AU122" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="123" spans="47:47">
       <c r="AU123" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="124" spans="47:47">
       <c r="AU124" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="125" spans="47:47">
       <c r="AU125" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="126" spans="47:47">
       <c r="AU126" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="127" spans="47:47">
       <c r="AU127" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="128" spans="47:47">
       <c r="AU128" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="129" spans="47:47">
       <c r="AU129" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="130" spans="47:47">
       <c r="AU130" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="131" spans="47:47">
       <c r="AU131" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="132" spans="47:47">
       <c r="AU132" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="133" spans="47:47">
       <c r="AU133" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="134" spans="47:47">
       <c r="AU134" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="135" spans="47:47">
       <c r="AU135" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="136" spans="47:47">
       <c r="AU136" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="137" spans="47:47">
       <c r="AU137" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="138" spans="47:47">
       <c r="AU138" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="139" spans="47:47">
       <c r="AU139" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="140" spans="47:47">
       <c r="AU140" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="141" spans="47:47">
       <c r="AU141" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="142" spans="47:47">
       <c r="AU142" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="143" spans="47:47">
       <c r="AU143" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="144" spans="47:47">
       <c r="AU144" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="145" spans="47:47">
       <c r="AU145" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="146" spans="47:47">
       <c r="AU146" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="147" spans="47:47">
       <c r="AU147" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="148" spans="47:47">
       <c r="AU148" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="149" spans="47:47">
       <c r="AU149" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="150" spans="47:47">
       <c r="AU150" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="151" spans="47:47">
       <c r="AU151" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="152" spans="47:47">
       <c r="AU152" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="153" spans="47:47">
       <c r="AU153" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="154" spans="47:47">
       <c r="AU154" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="155" spans="47:47">
       <c r="AU155" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="156" spans="47:47">
       <c r="AU156" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="157" spans="47:47">
       <c r="AU157" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="158" spans="47:47">
       <c r="AU158" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="159" spans="47:47">
       <c r="AU159" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="160" spans="47:47">
       <c r="AU160" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="47:47">
       <c r="AU161" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162" spans="47:47">
       <c r="AU162" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="163" spans="47:47">
       <c r="AU163" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="164" spans="47:47">
       <c r="AU164" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="165" spans="47:47">
       <c r="AU165" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="166" spans="47:47">
       <c r="AU166" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="167" spans="47:47">
       <c r="AU167" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="168" spans="47:47">
       <c r="AU168" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="169" spans="47:47">
       <c r="AU169" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="170" spans="47:47">
       <c r="AU170" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="171" spans="47:47">
       <c r="AU171" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="172" spans="47:47">
       <c r="AU172" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="173" spans="47:47">
       <c r="AU173" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="174" spans="47:47">
       <c r="AU174" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="175" spans="47:47">
       <c r="AU175" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="176" spans="47:47">
       <c r="AU176" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="177" spans="47:47">
       <c r="AU177" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="178" spans="47:47">
       <c r="AU178" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="179" spans="47:47">
       <c r="AU179" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="180" spans="47:47">
       <c r="AU180" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="181" spans="47:47">
       <c r="AU181" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="182" spans="47:47">
       <c r="AU182" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="183" spans="47:47">
       <c r="AU183" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="184" spans="47:47">
       <c r="AU184" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="185" spans="47:47">
       <c r="AU185" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="186" spans="47:47">
       <c r="AU186" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="187" spans="47:47">
       <c r="AU187" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="188" spans="47:47">
       <c r="AU188" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="189" spans="47:47">
       <c r="AU189" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="190" spans="47:47">
       <c r="AU190" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="191" spans="47:47">
       <c r="AU191" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="192" spans="47:47">
       <c r="AU192" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="193" spans="47:47">
       <c r="AU193" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="194" spans="47:47">
       <c r="AU194" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="195" spans="47:47">
       <c r="AU195" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="196" spans="47:47">
       <c r="AU196" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="197" spans="47:47">
       <c r="AU197" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="198" spans="47:47">
       <c r="AU198" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="199" spans="47:47">
       <c r="AU199" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="200" spans="47:47">
       <c r="AU200" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="201" spans="47:47">
       <c r="AU201" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="202" spans="47:47">
       <c r="AU202" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="203" spans="47:47">
       <c r="AU203" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="204" spans="47:47">
       <c r="AU204" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="205" spans="47:47">
       <c r="AU205" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="206" spans="47:47">
       <c r="AU206" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="207" spans="47:47">
       <c r="AU207" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="208" spans="47:47">
       <c r="AU208" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="209" spans="47:47">
       <c r="AU209" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="210" spans="47:47">
       <c r="AU210" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="211" spans="47:47">
       <c r="AU211" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="212" spans="47:47">
       <c r="AU212" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="213" spans="47:47">
       <c r="AU213" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="214" spans="47:47">
       <c r="AU214" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="215" spans="47:47">
       <c r="AU215" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="216" spans="47:47">
       <c r="AU216" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="217" spans="47:47">
       <c r="AU217" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="218" spans="47:47">
       <c r="AU218" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="219" spans="47:47">
       <c r="AU219" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="220" spans="47:47">
       <c r="AU220" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="221" spans="47:47">
       <c r="AU221" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="222" spans="47:47">
       <c r="AU222" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="223" spans="47:47">
       <c r="AU223" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="224" spans="47:47">
       <c r="AU224" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="225" spans="47:47">
       <c r="AU225" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="226" spans="47:47">
       <c r="AU226" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="227" spans="47:47">
       <c r="AU227" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="228" spans="47:47">
       <c r="AU228" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="229" spans="47:47">
       <c r="AU229" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="230" spans="47:47">
       <c r="AU230" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="231" spans="47:47">
       <c r="AU231" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="232" spans="47:47">
       <c r="AU232" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="233" spans="47:47">
       <c r="AU233" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="234" spans="47:47">
       <c r="AU234" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="235" spans="47:47">
       <c r="AU235" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="236" spans="47:47">
       <c r="AU236" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="237" spans="47:47">
       <c r="AU237" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="238" spans="47:47">
       <c r="AU238" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="239" spans="47:47">
       <c r="AU239" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="240" spans="47:47">
       <c r="AU240" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="241" spans="47:47">
       <c r="AU241" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="242" spans="47:47">
       <c r="AU242" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="243" spans="47:47">
       <c r="AU243" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="244" spans="47:47">
       <c r="AU244" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="245" spans="47:47">
       <c r="AU245" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="246" spans="47:47">
       <c r="AU246" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="247" spans="47:47">
       <c r="AU247" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="248" spans="47:47">
       <c r="AU248" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="249" spans="47:47">
       <c r="AU249" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="250" spans="47:47">
       <c r="AU250" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="251" spans="47:47">
       <c r="AU251" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="252" spans="47:47">
       <c r="AU252" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="253" spans="47:47">
       <c r="AU253" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="254" spans="47:47">
       <c r="AU254" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="255" spans="47:47">
       <c r="AU255" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="256" spans="47:47">
       <c r="AU256" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="257" spans="47:47">
       <c r="AU257" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="258" spans="47:47">
       <c r="AU258" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="259" spans="47:47">
       <c r="AU259" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="260" spans="47:47">
       <c r="AU260" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="261" spans="47:47">
       <c r="AU261" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="262" spans="47:47">
       <c r="AU262" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="263" spans="47:47">
       <c r="AU263" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="264" spans="47:47">
       <c r="AU264" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="265" spans="47:47">
       <c r="AU265" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="266" spans="47:47">
       <c r="AU266" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="267" spans="47:47">
       <c r="AU267" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="268" spans="47:47">
       <c r="AU268" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="269" spans="47:47">
       <c r="AU269" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="270" spans="47:47">
       <c r="AU270" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="271" spans="47:47">
       <c r="AU271" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="272" spans="47:47">
       <c r="AU272" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="273" spans="47:47">
       <c r="AU273" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="274" spans="47:47">
       <c r="AU274" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="275" spans="47:47">
       <c r="AU275" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="276" spans="47:47">
       <c r="AU276" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="277" spans="47:47">
       <c r="AU277" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="278" spans="47:47">
       <c r="AU278" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="279" spans="47:47">
       <c r="AU279" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="280" spans="47:47">
       <c r="AU280" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="281" spans="47:47">
       <c r="AU281" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="282" spans="47:47">
       <c r="AU282" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="283" spans="47:47">
       <c r="AU283" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="284" spans="47:47">
       <c r="AU284" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="285" spans="47:47">
       <c r="AU285" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="286" spans="47:47">
       <c r="AU286" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="287" spans="47:47">
       <c r="AU287" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="288" spans="47:47">
       <c r="AU288" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="289" spans="47:47">
       <c r="AU289" t="s">
-        <v>656</v>
+        <v>658</v>
+      </c>
+    </row>
+    <row r="290" spans="47:47">
+      <c r="AU290" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="291" spans="47:47">
+      <c r="AU291" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="292" spans="47:47">
+      <c r="AU292" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="293" spans="47:47">
+      <c r="AU293" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="294" spans="47:47">
+      <c r="AU294" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000047/metadata_template_ERC000047.xlsx
+++ b/templates/ERC000047/metadata_template_ERC000047.xlsx
@@ -21,7 +21,7 @@
     <definedName name="contaminationscreeninginput">'cv_sample'!$Z$1:$Z$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="699">
   <si>
     <t>alias</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2658,7 +2661,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2702,7 +2705,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2729,7 +2732,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3466,6 +3469,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3487,27 +3495,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3527,122 +3535,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3666,378 +3674,378 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:63" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -4072,1520 +4080,1520 @@
   <sheetData>
     <row r="1" spans="7:47">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AD1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AF1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AU1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="7:47">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AD2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AF2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AU2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="7:47">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AF3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AU3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="7:47">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AU4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="7:47">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AU5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="7:47">
       <c r="G6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AU6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="7:47">
       <c r="G7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AU7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="7:47">
       <c r="AU8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="7:47">
       <c r="AU9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="7:47">
       <c r="AU10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="7:47">
       <c r="AU11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="7:47">
       <c r="AU12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="7:47">
       <c r="AU13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="7:47">
       <c r="AU14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="7:47">
       <c r="AU15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" spans="7:47">
       <c r="AU16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="47:47">
       <c r="AU17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="47:47">
       <c r="AU18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="47:47">
       <c r="AU19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="47:47">
       <c r="AU20" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="47:47">
       <c r="AU21" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="47:47">
       <c r="AU22" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" spans="47:47">
       <c r="AU23" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" spans="47:47">
       <c r="AU24" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="47:47">
       <c r="AU25" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="47:47">
       <c r="AU26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="47:47">
       <c r="AU27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" spans="47:47">
       <c r="AU28" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29" spans="47:47">
       <c r="AU29" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30" spans="47:47">
       <c r="AU30" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="47:47">
       <c r="AU31" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="47:47">
       <c r="AU32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="47:47">
       <c r="AU33" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="47:47">
       <c r="AU34" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="47:47">
       <c r="AU35" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36" spans="47:47">
       <c r="AU36" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="37" spans="47:47">
       <c r="AU37" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="47:47">
       <c r="AU38" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="47:47">
       <c r="AU39" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" spans="47:47">
       <c r="AU40" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" spans="47:47">
       <c r="AU41" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="42" spans="47:47">
       <c r="AU42" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="47:47">
       <c r="AU43" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="44" spans="47:47">
       <c r="AU44" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="45" spans="47:47">
       <c r="AU45" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="46" spans="47:47">
       <c r="AU46" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="47:47">
       <c r="AU47" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="47:47">
       <c r="AU48" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="49" spans="47:47">
       <c r="AU49" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" spans="47:47">
       <c r="AU50" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="51" spans="47:47">
       <c r="AU51" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="52" spans="47:47">
       <c r="AU52" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="53" spans="47:47">
       <c r="AU53" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="54" spans="47:47">
       <c r="AU54" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55" spans="47:47">
       <c r="AU55" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" spans="47:47">
       <c r="AU56" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" spans="47:47">
       <c r="AU57" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="47:47">
       <c r="AU58" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="47:47">
       <c r="AU59" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="60" spans="47:47">
       <c r="AU60" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" spans="47:47">
       <c r="AU61" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="62" spans="47:47">
       <c r="AU62" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="63" spans="47:47">
       <c r="AU63" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="47:47">
       <c r="AU64" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="65" spans="47:47">
       <c r="AU65" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="66" spans="47:47">
       <c r="AU66" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="67" spans="47:47">
       <c r="AU67" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="68" spans="47:47">
       <c r="AU68" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="69" spans="47:47">
       <c r="AU69" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="70" spans="47:47">
       <c r="AU70" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="71" spans="47:47">
       <c r="AU71" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="72" spans="47:47">
       <c r="AU72" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="73" spans="47:47">
       <c r="AU73" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="74" spans="47:47">
       <c r="AU74" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="75" spans="47:47">
       <c r="AU75" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76" spans="47:47">
       <c r="AU76" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="77" spans="47:47">
       <c r="AU77" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="78" spans="47:47">
       <c r="AU78" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79" spans="47:47">
       <c r="AU79" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="80" spans="47:47">
       <c r="AU80" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="81" spans="47:47">
       <c r="AU81" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="82" spans="47:47">
       <c r="AU82" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="83" spans="47:47">
       <c r="AU83" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="84" spans="47:47">
       <c r="AU84" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="85" spans="47:47">
       <c r="AU85" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="86" spans="47:47">
       <c r="AU86" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="87" spans="47:47">
       <c r="AU87" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="88" spans="47:47">
       <c r="AU88" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="89" spans="47:47">
       <c r="AU89" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="90" spans="47:47">
       <c r="AU90" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="91" spans="47:47">
       <c r="AU91" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="92" spans="47:47">
       <c r="AU92" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="93" spans="47:47">
       <c r="AU93" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="94" spans="47:47">
       <c r="AU94" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="95" spans="47:47">
       <c r="AU95" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="96" spans="47:47">
       <c r="AU96" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="97" spans="47:47">
       <c r="AU97" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="98" spans="47:47">
       <c r="AU98" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="99" spans="47:47">
       <c r="AU99" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="100" spans="47:47">
       <c r="AU100" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="101" spans="47:47">
       <c r="AU101" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="102" spans="47:47">
       <c r="AU102" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="103" spans="47:47">
       <c r="AU103" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="104" spans="47:47">
       <c r="AU104" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="105" spans="47:47">
       <c r="AU105" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="106" spans="47:47">
       <c r="AU106" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="107" spans="47:47">
       <c r="AU107" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="108" spans="47:47">
       <c r="AU108" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="109" spans="47:47">
       <c r="AU109" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="110" spans="47:47">
       <c r="AU110" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="47:47">
       <c r="AU111" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="112" spans="47:47">
       <c r="AU112" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="113" spans="47:47">
       <c r="AU113" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="114" spans="47:47">
       <c r="AU114" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="115" spans="47:47">
       <c r="AU115" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="116" spans="47:47">
       <c r="AU116" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117" spans="47:47">
       <c r="AU117" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="118" spans="47:47">
       <c r="AU118" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="119" spans="47:47">
       <c r="AU119" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="120" spans="47:47">
       <c r="AU120" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="121" spans="47:47">
       <c r="AU121" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="122" spans="47:47">
       <c r="AU122" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="123" spans="47:47">
       <c r="AU123" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="124" spans="47:47">
       <c r="AU124" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="125" spans="47:47">
       <c r="AU125" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="126" spans="47:47">
       <c r="AU126" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="127" spans="47:47">
       <c r="AU127" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="128" spans="47:47">
       <c r="AU128" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="129" spans="47:47">
       <c r="AU129" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="130" spans="47:47">
       <c r="AU130" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131" spans="47:47">
       <c r="AU131" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="132" spans="47:47">
       <c r="AU132" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="133" spans="47:47">
       <c r="AU133" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="134" spans="47:47">
       <c r="AU134" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="135" spans="47:47">
       <c r="AU135" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="136" spans="47:47">
       <c r="AU136" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="137" spans="47:47">
       <c r="AU137" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="138" spans="47:47">
       <c r="AU138" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="139" spans="47:47">
       <c r="AU139" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="140" spans="47:47">
       <c r="AU140" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="141" spans="47:47">
       <c r="AU141" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="142" spans="47:47">
       <c r="AU142" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="143" spans="47:47">
       <c r="AU143" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="144" spans="47:47">
       <c r="AU144" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="145" spans="47:47">
       <c r="AU145" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="146" spans="47:47">
       <c r="AU146" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="147" spans="47:47">
       <c r="AU147" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="148" spans="47:47">
       <c r="AU148" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="149" spans="47:47">
       <c r="AU149" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="150" spans="47:47">
       <c r="AU150" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="151" spans="47:47">
       <c r="AU151" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="152" spans="47:47">
       <c r="AU152" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="153" spans="47:47">
       <c r="AU153" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="154" spans="47:47">
       <c r="AU154" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="155" spans="47:47">
       <c r="AU155" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="156" spans="47:47">
       <c r="AU156" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="157" spans="47:47">
       <c r="AU157" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="158" spans="47:47">
       <c r="AU158" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="159" spans="47:47">
       <c r="AU159" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="160" spans="47:47">
       <c r="AU160" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="161" spans="47:47">
       <c r="AU161" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="162" spans="47:47">
       <c r="AU162" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="163" spans="47:47">
       <c r="AU163" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="164" spans="47:47">
       <c r="AU164" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="165" spans="47:47">
       <c r="AU165" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="166" spans="47:47">
       <c r="AU166" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="167" spans="47:47">
       <c r="AU167" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="168" spans="47:47">
       <c r="AU168" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="169" spans="47:47">
       <c r="AU169" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="170" spans="47:47">
       <c r="AU170" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="171" spans="47:47">
       <c r="AU171" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="172" spans="47:47">
       <c r="AU172" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="173" spans="47:47">
       <c r="AU173" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="174" spans="47:47">
       <c r="AU174" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="175" spans="47:47">
       <c r="AU175" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="176" spans="47:47">
       <c r="AU176" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="177" spans="47:47">
       <c r="AU177" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="178" spans="47:47">
       <c r="AU178" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="179" spans="47:47">
       <c r="AU179" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="180" spans="47:47">
       <c r="AU180" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="181" spans="47:47">
       <c r="AU181" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="182" spans="47:47">
       <c r="AU182" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="183" spans="47:47">
       <c r="AU183" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="184" spans="47:47">
       <c r="AU184" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="185" spans="47:47">
       <c r="AU185" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="186" spans="47:47">
       <c r="AU186" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="187" spans="47:47">
       <c r="AU187" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="188" spans="47:47">
       <c r="AU188" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="189" spans="47:47">
       <c r="AU189" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="190" spans="47:47">
       <c r="AU190" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="191" spans="47:47">
       <c r="AU191" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="192" spans="47:47">
       <c r="AU192" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="193" spans="47:47">
       <c r="AU193" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="194" spans="47:47">
       <c r="AU194" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="195" spans="47:47">
       <c r="AU195" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="196" spans="47:47">
       <c r="AU196" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="197" spans="47:47">
       <c r="AU197" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="198" spans="47:47">
       <c r="AU198" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="199" spans="47:47">
       <c r="AU199" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="200" spans="47:47">
       <c r="AU200" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="201" spans="47:47">
       <c r="AU201" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="202" spans="47:47">
       <c r="AU202" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="203" spans="47:47">
       <c r="AU203" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="204" spans="47:47">
       <c r="AU204" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="205" spans="47:47">
       <c r="AU205" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="206" spans="47:47">
       <c r="AU206" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="207" spans="47:47">
       <c r="AU207" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="208" spans="47:47">
       <c r="AU208" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="209" spans="47:47">
       <c r="AU209" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="210" spans="47:47">
       <c r="AU210" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="211" spans="47:47">
       <c r="AU211" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="212" spans="47:47">
       <c r="AU212" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="213" spans="47:47">
       <c r="AU213" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="214" spans="47:47">
       <c r="AU214" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="215" spans="47:47">
       <c r="AU215" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="216" spans="47:47">
       <c r="AU216" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="217" spans="47:47">
       <c r="AU217" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="218" spans="47:47">
       <c r="AU218" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="219" spans="47:47">
       <c r="AU219" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="220" spans="47:47">
       <c r="AU220" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="221" spans="47:47">
       <c r="AU221" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="222" spans="47:47">
       <c r="AU222" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="223" spans="47:47">
       <c r="AU223" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="224" spans="47:47">
       <c r="AU224" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="225" spans="47:47">
       <c r="AU225" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="226" spans="47:47">
       <c r="AU226" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="227" spans="47:47">
       <c r="AU227" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="228" spans="47:47">
       <c r="AU228" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="229" spans="47:47">
       <c r="AU229" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="230" spans="47:47">
       <c r="AU230" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="231" spans="47:47">
       <c r="AU231" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="232" spans="47:47">
       <c r="AU232" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="233" spans="47:47">
       <c r="AU233" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="234" spans="47:47">
       <c r="AU234" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="235" spans="47:47">
       <c r="AU235" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="236" spans="47:47">
       <c r="AU236" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="237" spans="47:47">
       <c r="AU237" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="238" spans="47:47">
       <c r="AU238" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="239" spans="47:47">
       <c r="AU239" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="240" spans="47:47">
       <c r="AU240" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="241" spans="47:47">
       <c r="AU241" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="242" spans="47:47">
       <c r="AU242" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="243" spans="47:47">
       <c r="AU243" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="244" spans="47:47">
       <c r="AU244" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="245" spans="47:47">
       <c r="AU245" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="246" spans="47:47">
       <c r="AU246" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="247" spans="47:47">
       <c r="AU247" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="248" spans="47:47">
       <c r="AU248" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="249" spans="47:47">
       <c r="AU249" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="250" spans="47:47">
       <c r="AU250" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="251" spans="47:47">
       <c r="AU251" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="252" spans="47:47">
       <c r="AU252" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="253" spans="47:47">
       <c r="AU253" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="254" spans="47:47">
       <c r="AU254" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="255" spans="47:47">
       <c r="AU255" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="256" spans="47:47">
       <c r="AU256" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="257" spans="47:47">
       <c r="AU257" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="258" spans="47:47">
       <c r="AU258" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="259" spans="47:47">
       <c r="AU259" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="260" spans="47:47">
       <c r="AU260" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="261" spans="47:47">
       <c r="AU261" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="262" spans="47:47">
       <c r="AU262" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="263" spans="47:47">
       <c r="AU263" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="264" spans="47:47">
       <c r="AU264" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="265" spans="47:47">
       <c r="AU265" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="266" spans="47:47">
       <c r="AU266" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="267" spans="47:47">
       <c r="AU267" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="268" spans="47:47">
       <c r="AU268" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="269" spans="47:47">
       <c r="AU269" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="270" spans="47:47">
       <c r="AU270" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="271" spans="47:47">
       <c r="AU271" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="272" spans="47:47">
       <c r="AU272" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="273" spans="47:47">
       <c r="AU273" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="274" spans="47:47">
       <c r="AU274" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="275" spans="47:47">
       <c r="AU275" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="276" spans="47:47">
       <c r="AU276" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="277" spans="47:47">
       <c r="AU277" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="278" spans="47:47">
       <c r="AU278" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="279" spans="47:47">
       <c r="AU279" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="280" spans="47:47">
       <c r="AU280" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="281" spans="47:47">
       <c r="AU281" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="282" spans="47:47">
       <c r="AU282" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="283" spans="47:47">
       <c r="AU283" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="284" spans="47:47">
       <c r="AU284" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="285" spans="47:47">
       <c r="AU285" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="286" spans="47:47">
       <c r="AU286" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="287" spans="47:47">
       <c r="AU287" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="288" spans="47:47">
       <c r="AU288" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="289" spans="47:47">
       <c r="AU289" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="290" spans="47:47">
       <c r="AU290" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="291" spans="47:47">
       <c r="AU291" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="292" spans="47:47">
       <c r="AU292" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="293" spans="47:47">
       <c r="AU293" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="294" spans="47:47">
       <c r="AU294" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>
